--- a/docs/SEM_Composition_TAPP_v4.xlsx
+++ b/docs/SEM_Composition_TAPP_v4.xlsx
@@ -2,12 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="120" yWindow="3000" windowWidth="28515" windowHeight="8970" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legends" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,30 +47,35 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFC00000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF0070C0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF7030A0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF375623"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF000000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -83,7 +91,7 @@
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -117,21 +125,26 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -192,11 +205,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -269,7 +282,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -459,6 +472,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -469,21 +484,21 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AY86"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="38" customWidth="1" style="21" min="1" max="1"/>
-    <col width="68" customWidth="1" style="21" min="2" max="2"/>
-    <col width="15" customWidth="1" style="21" min="3" max="4"/>
-    <col width="20" customWidth="1" style="21" min="5" max="5"/>
-    <col width="48" customWidth="1" style="21" min="6" max="6"/>
-    <col width="22" customWidth="1" style="21" min="7" max="7"/>
-    <col width="14" customWidth="1" style="21" min="8" max="8"/>
-    <col width="13" customWidth="1" style="21" min="9" max="12"/>
-    <col width="4" customWidth="1" style="21" min="13" max="13"/>
-    <col width="30" customWidth="1" style="21" min="14" max="48"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="48"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32.25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metadata Item</t>
@@ -954,7 +969,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Protocol Name</t>
@@ -1202,7 +1217,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Technique</t>
@@ -1456,7 +1471,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Protocol Author</t>
@@ -1704,7 +1719,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="75" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Laboratory</t>
@@ -2448,7 +2463,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Funding Source for Protocol Development</t>
@@ -2701,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
           <t>Protocol Reference(s)</t>
@@ -2954,7 +2969,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Protocol DOI</t>
@@ -3926,7 +3941,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>Funding Source for Analysis</t>
@@ -4169,7 +4184,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="90" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Coupled Technique(s)</t>
@@ -4423,7 +4438,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="75" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
           <t>Coupling Description</t>
@@ -4674,7 +4689,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Coupled Protocol DOI</t>
@@ -4917,7 +4932,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>Coupled Dataset or Publication Reference</t>
@@ -5374,7 +5389,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Target Material</t>
@@ -5628,7 +5643,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="21">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
           <t>Sample Preparation Method</t>
@@ -5881,7 +5896,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="21">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
           <t>Sample Name</t>
@@ -6124,7 +6139,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="21">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Sample Persistent Identifier</t>
@@ -6367,7 +6382,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="21">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>3. Instrument &amp; Software</t>
@@ -6581,7 +6596,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="21">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
           <t>Instrument Manufacturer</t>
@@ -6829,7 +6844,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="21">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
           <t>Instrument Model</t>
@@ -7077,7 +7092,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="21">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
           <t>Electron Source</t>
@@ -7325,7 +7340,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1" s="21">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
           <t>Instrument Variant</t>
@@ -7563,7 +7578,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="21">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
           <t>EDS Detector Configuration</t>
@@ -7820,7 +7835,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="21">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
           <t>WDS Spectrometer Configuration</t>
@@ -8077,7 +8092,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="21">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
           <t>Acquisition Software</t>
@@ -8330,7 +8345,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="21">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
           <t>Data Reduction Software</t>
@@ -8583,7 +8598,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1" s="21">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>4. Measurement Information</t>
@@ -8797,7 +8812,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1" s="21">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
           <t>Analytical Mode</t>
@@ -9040,7 +9055,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="21">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
           <t>Beam Mode</t>
@@ -9155,7 +9170,7 @@
       <c r="AX36" s="1" t="n"/>
       <c r="AY36" s="1" t="n"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1" s="21">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
           <t>Accelerating Voltage</t>
@@ -9393,7 +9408,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="21">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Beam Current</t>
@@ -9635,7 +9650,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1" s="21">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
           <t>Beam Diameter</t>
@@ -9733,7 +9748,7 @@
       <c r="AX39" s="1" t="n"/>
       <c r="AY39" s="1" t="n"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="21">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>Beam Raster Dimensions</t>
@@ -9848,7 +9863,7 @@
       <c r="AX40" s="1" t="n"/>
       <c r="AY40" s="1" t="n"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="21">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
           <t>Beam Damage Minimization</t>
@@ -9963,7 +9978,7 @@
       <c r="AX41" s="1" t="n"/>
       <c r="AY41" s="1" t="n"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="21">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
           <t>Drift Correction</t>
@@ -10078,7 +10093,7 @@
       <c r="AX42" s="1" t="n"/>
       <c r="AY42" s="1" t="n"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="21">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
           <t>Stage Scan vs. Beam Scan</t>
@@ -10176,7 +10191,7 @@
       <c r="AX43" s="1" t="n"/>
       <c r="AY43" s="1" t="n"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1" s="21">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
           <t>Working Distance</t>
@@ -10414,7 +10429,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="21">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
           <t>Chamber Pressure</t>
@@ -10652,7 +10667,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="21">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
           <t>Dwell Time per Pixel</t>
@@ -10686,705 +10701,705 @@
       <c r="G46" s="1" t="n"/>
       <c r="H46" s="1" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P46" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AC46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AD46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AE46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AG46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AI46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AJ46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AK46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AM46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AN46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AO46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AP46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AQ46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AR46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AS46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AV46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AW46" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AX46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>EDS Acquisition Mode</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>Spatial acquisition sub-strategy for EDS measurements: stationary-beam point acquisition, linescan (beam stepped along a transect at defined intervals), or area map (beam rastered over a pixel grid). Specifies how the beam is positioned during data collection within the declared Analytical Mode. Particularly important when a protocol includes linescans as a distinct acquisition approach not fully captured by the mode flag columns.</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>Controlled list</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>Point / spot | Line scan | Map | Automated mineralogy | Multiple (specify) | Other: specify | N/A | None</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>EDS specific</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J46" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P46" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="T46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Z46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AA46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AB46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AC46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AD46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AE46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AG46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AH46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AI46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AJ46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AK46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AL46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AM46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AN46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AO46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AP46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AQ46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AR46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AS46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AT46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AU46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AV46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AW46" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AX46" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AY46" s="1" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P47" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T47" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W47" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z47" s="1" t="inlineStr">
+        <is>
+          <t>Map</t>
+        </is>
+      </c>
+      <c r="AA47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB47" s="1" t="inlineStr">
+        <is>
+          <t>Point / spot; Map</t>
+        </is>
+      </c>
+      <c r="AC47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AI47" s="1" t="inlineStr">
+        <is>
+          <t>Spot analysis</t>
+        </is>
+      </c>
+      <c r="AJ47" s="1" t="inlineStr">
+        <is>
+          <t>Element mapping</t>
+        </is>
+      </c>
+      <c r="AK47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AL47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AM47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AN47" s="1" t="inlineStr">
+        <is>
+          <t>Point spectra (spot analysis)</t>
+        </is>
+      </c>
+      <c r="AO47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AP47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AQ47" s="1" t="inlineStr">
+        <is>
+          <t>EDS mapping</t>
+        </is>
+      </c>
+      <c r="AR47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AS47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AV47" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AW47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AX47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY47" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="21">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>EDS Acquisition Mode</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>Spatial acquisition sub-strategy for EDS measurements: stationary-beam point acquisition, linescan (beam stepped along a transect at defined intervals), or area map (beam rastered over a pixel grid). Specifies how the beam is positioned during data collection within the declared Analytical Mode. Particularly important when a protocol includes linescans as a distinct acquisition approach not fully captured by the mode flag columns.</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Analyte</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>Element(s) measured by this protocol. The protocol registers the full intended analyte suite; analysts record the specific subset measured in a given session, which may be narrower. Fields below flagged as Analyte-Specific in the Comments column apply individually to each element in this list.</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Read-Only</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>Controlled list</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>Point / spot | Line scan | Map | Automated mineralogy | Multiple (specify) | Other: specify | N/A | None</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>EDS specific</t>
-        </is>
-      </c>
-      <c r="H47" s="1" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J47" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L47" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P47" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T47" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W47" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Z47" s="1" t="inlineStr">
-        <is>
-          <t>Map</t>
-        </is>
-      </c>
-      <c r="AA47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AB47" s="1" t="inlineStr">
-        <is>
-          <t>Point / spot; Map</t>
-        </is>
-      </c>
-      <c r="AC47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AD47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AE47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AF47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AG47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AH47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI47" s="1" t="inlineStr">
-        <is>
-          <t>Spot analysis</t>
-        </is>
-      </c>
-      <c r="AJ47" s="1" t="inlineStr">
-        <is>
-          <t>Element mapping</t>
-        </is>
-      </c>
-      <c r="AK47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AL47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AM47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AN47" s="1" t="inlineStr">
-        <is>
-          <t>Point spectra (spot analysis)</t>
-        </is>
-      </c>
-      <c r="AO47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AP47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AQ47" s="1" t="inlineStr">
-        <is>
-          <t>EDS mapping</t>
-        </is>
-      </c>
-      <c r="AR47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AS47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AT47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AU47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AV47" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AW47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AX47" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AY47" s="1" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Editable</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>Text (free)</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>e.g., 'Si, Al, Fe, Mg, Ca, Na, K, Ti, Cr, Mn, Ni, S'</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>Analyte-Specific</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:analytes</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>list of target analytes</t>
+        </is>
+      </c>
+      <c r="P48" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T48" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W48" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z48" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB48" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AC48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AI48" s="1" t="inlineStr">
+        <is>
+          <t>Mg, Si, Fe, Ni, S, Na, Ca, Al</t>
+        </is>
+      </c>
+      <c r="AJ48" s="1" t="inlineStr">
+        <is>
+          <t>Mg, Si, Fe, Ni, S, Na, Ca, Al (element mapping)</t>
+        </is>
+      </c>
+      <c r="AK48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AL48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AM48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AN48" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AO48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AP48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AQ48" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AR48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AS48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AV48" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AW48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AX48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY48" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1" s="21">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>Analyte</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>Element(s) measured by this protocol. The protocol registers the full intended analyte suite; analysts record the specific subset measured in a given session, which may be narrower. Fields below flagged as Analyte-Specific in the Comments column apply individually to each element in this list.</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>Editable</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>Text (free)</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>e.g., 'Si, Al, Fe, Mg, Ca, Na, K, Ti, Cr, Mn, Ni, S'</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>Analyte-Specific</t>
-        </is>
-      </c>
-      <c r="H48" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J48" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K48" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L48" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>$MethodDefinition.ada:analytes</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>list of target analytes</t>
-        </is>
-      </c>
-      <c r="P48" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T48" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W48" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Z48" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AB48" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AC48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AD48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AE48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AF48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AG48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AH48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI48" s="1" t="inlineStr">
-        <is>
-          <t>Mg, Si, Fe, Ni, S, Na, Ca, Al</t>
-        </is>
-      </c>
-      <c r="AJ48" s="1" t="inlineStr">
-        <is>
-          <t>Mg, Si, Fe, Ni, S, Na, Ca, Al (element mapping)</t>
-        </is>
-      </c>
-      <c r="AK48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AL48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AM48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AN48" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AO48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AP48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AQ48" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AS48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AT48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AU48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AV48" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AW48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AX48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AY48" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" s="21">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
           <t>Technique per Analyte</t>
@@ -11482,7 +11497,7 @@
       <c r="AX49" s="1" t="n"/>
       <c r="AY49" s="1" t="n"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" s="21">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
           <t>X-ray Line</t>
@@ -11741,7 +11756,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1" s="21">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
           <t>EDS Live Time per Point or Pixel</t>
@@ -11983,7 +11998,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1" s="21">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
           <t>Step Size / Pixel Size</t>
@@ -12225,7 +12240,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1" s="21">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
           <t>EDS Map Dimensions</t>
@@ -12467,7 +12482,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1" s="21">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
           <t>Map Area</t>
@@ -12565,7 +12580,7 @@
       <c r="AX54" s="1" t="n"/>
       <c r="AY54" s="1" t="n"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1" s="21">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
           <t>Diffracting Crystal</t>
@@ -12824,7 +12839,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1" s="21">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
           <t>WDS Spectrometer Channel</t>
@@ -13083,7 +13098,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1" s="21">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
           <t>Sequence</t>
@@ -13342,7 +13357,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1" s="21">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
           <t>Proportional Counter / Detector</t>
@@ -13601,7 +13616,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1" s="21">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
           <t>WDS PHA Setting</t>
@@ -13860,7 +13875,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1" s="21">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
           <t>Peak Counting Time</t>
@@ -13898,695 +13913,695 @@
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J60" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L60" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P60" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AC60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AI60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AJ60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AK60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AL60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AM60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AN60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AO60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AP60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AQ60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AR60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AS60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AV60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AW60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AX60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>Background Counting Time</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>Total time spent counting at off-peak background position(s) in seconds, summed across all background positions.</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Editable</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>Numeric (s)</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>e.g., 5 | 10 | 20</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>SEM-WDS specific; Analyte-Specific</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K61" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L61" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P61" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AC61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AI61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AJ61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AK61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AL61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AM61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AN61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AO61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AP61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AQ61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AR61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AS61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AV61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AW61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AX61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY61" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="36.75" customHeight="1">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>Background Position(s)</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>Location(s) of off-peak background measurement(s) relative to the peak, in mm or sin-theta, and whether on the high- or low-energy side.</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Editable</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>Numeric + label</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>e.g., '+5 mm (High), -5 mm (Low)' | 'High only (+4 mm)' | 'MAN method (no off-peak positions)'</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>SEM-WDS specific; Analyte-Specific</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="inlineStr">
+        <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J60" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K60" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L60" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P60" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Z60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AA60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AB60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AC60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AD60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AE60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AF60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AG60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AH60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AJ60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AK60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AL60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AM60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AN60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AO60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AP60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AQ60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AR60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AS60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AT60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AU60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AV60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AW60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AX60" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AY60" s="1" t="inlineStr">
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L62" s="13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P62" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AA62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AC62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AI62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AJ62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AK62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AL62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AM62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AN62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AO62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AP62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AQ62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AR62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AS62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AV62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AW62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AX62" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AY62" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1" s="21">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>Background Counting Time</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>Total time spent counting at off-peak background position(s) in seconds, summed across all background positions.</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>Editable</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>Numeric (s)</t>
-        </is>
-      </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>e.g., 5 | 10 | 20</t>
-        </is>
-      </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>SEM-WDS specific; Analyte-Specific</t>
-        </is>
-      </c>
-      <c r="H61" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J61" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K61" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L61" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P61" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Z61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AA61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AB61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AC61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AD61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AE61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AF61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AG61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AH61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AJ61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AK61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AL61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AM61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AN61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AO61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AP61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AQ61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AR61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AS61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AT61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AU61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AV61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AW61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AX61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AY61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1" s="21">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>Background Position(s)</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>Location(s) of off-peak background measurement(s) relative to the peak, in mm or sin-theta, and whether on the high- or low-energy side.</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>Advanced</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>Editable</t>
-        </is>
-      </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>Numeric + label</t>
-        </is>
-      </c>
-      <c r="F62" s="1" t="inlineStr">
-        <is>
-          <t>e.g., '+5 mm (High), -5 mm (Low)' | 'High only (+4 mm)' | 'MAN method (no off-peak positions)'</t>
-        </is>
-      </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>SEM-WDS specific; Analyte-Specific</t>
-        </is>
-      </c>
-      <c r="H62" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J62" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K62" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L62" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P62" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Z62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AA62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AB62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AC62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AD62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AE62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AF62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AG62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AH62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AJ62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AK62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AL62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AM62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AN62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AO62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AP62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AQ62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AR62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AS62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AT62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AU62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AV62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AW62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AX62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AY62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1" s="21">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
           <t>5. Data Processing</t>
@@ -14800,7 +14815,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1" s="21">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
           <t>Matrix Correction Method</t>
@@ -15055,7 +15070,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="15.75" customHeight="1" s="21">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
           <t>Mass Absorption Coefficients (MACs)</t>
@@ -15310,7 +15325,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1" s="21">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
           <t>Background Correction Method</t>
@@ -15569,7 +15584,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1" s="21">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
           <t>Time-Dependent Intensity Correction</t>
@@ -15828,7 +15843,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="15.75" customHeight="1" s="21">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
           <t>Analyte Estimation Method</t>
@@ -16070,7 +16085,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="15.75" customHeight="1" s="21">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
           <t>Halogen Correction on Oxygen</t>
@@ -16329,7 +16344,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1" s="21">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
           <t>EDS Spectral Processing Type</t>
@@ -16588,7 +16603,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="15.75" customHeight="1" s="21">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
           <t>Blank Correction</t>
@@ -16847,7 +16862,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="15.75" customHeight="1" s="21">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
           <t>Normalization / Standards-Based Correction</t>
@@ -17102,7 +17117,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="15.75" customHeight="1" s="21">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
           <t>WDS Dead Time Correction</t>
@@ -17361,7 +17376,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="15.75" customHeight="1" s="21">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
           <t>6. Quality Control &amp; Uncertainty</t>
@@ -17575,7 +17590,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="15.75" customHeight="1" s="21">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
           <t>Primary Calibration Standard Name</t>
@@ -17832,7 +17847,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="15.75" customHeight="1" s="21">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
           <t>Secondary Reference Materials</t>
@@ -18089,7 +18104,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="15.75" customHeight="1" s="21">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
           <t>Interference Corrections Applied</t>
@@ -18348,7 +18363,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="15.75" customHeight="1" s="21">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
           <t>Interfering Elements</t>
@@ -18607,7 +18622,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="15.75" customHeight="1" s="21">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
           <t>Interference Correction Standard</t>
@@ -18866,7 +18881,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="15.75" customHeight="1" s="21">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
           <t>Detection Limit</t>
@@ -19120,7 +19135,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="15.75" customHeight="1" s="21">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
           <t>Detection Limit Method</t>
@@ -19374,7 +19389,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="15.75" customHeight="1" s="21">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
           <t>Analytical Precision</t>
@@ -19616,7 +19631,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="15.75" customHeight="1" s="21">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
           <t>Analytical Accuracy</t>
@@ -19858,7 +19873,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="15.75" customHeight="1" s="21">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
           <t>Counting Statistics Error</t>
@@ -20100,7 +20115,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="15.75" customHeight="1" s="21">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
           <t>EDS Dead Time</t>
@@ -20359,7 +20374,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="15.75" customHeight="1" s="21">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
           <t>Additional Notes</t>
@@ -20614,920 +20629,920 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="15.75" customHeight="1" s="21"/>
-    <row r="88" ht="15.75" customHeight="1" s="21"/>
-    <row r="89" ht="15.75" customHeight="1" s="21"/>
-    <row r="90" ht="15.75" customHeight="1" s="21"/>
-    <row r="91" ht="15.75" customHeight="1" s="21"/>
-    <row r="92" ht="15.75" customHeight="1" s="21"/>
-    <row r="93" ht="15.75" customHeight="1" s="21"/>
-    <row r="94" ht="15.75" customHeight="1" s="21"/>
-    <row r="95" ht="15.75" customHeight="1" s="21"/>
-    <row r="96" ht="15.75" customHeight="1" s="21"/>
-    <row r="97" ht="15.75" customHeight="1" s="21"/>
-    <row r="98" ht="15.75" customHeight="1" s="21"/>
-    <row r="99" ht="15.75" customHeight="1" s="21"/>
-    <row r="100" ht="15.75" customHeight="1" s="21"/>
-    <row r="101" ht="15.75" customHeight="1" s="21"/>
-    <row r="102" ht="15.75" customHeight="1" s="21"/>
-    <row r="103" ht="15.75" customHeight="1" s="21"/>
-    <row r="104" ht="15.75" customHeight="1" s="21"/>
-    <row r="105" ht="15.75" customHeight="1" s="21"/>
-    <row r="106" ht="15.75" customHeight="1" s="21"/>
-    <row r="107" ht="15.75" customHeight="1" s="21"/>
-    <row r="108" ht="15.75" customHeight="1" s="21"/>
-    <row r="109" ht="15.75" customHeight="1" s="21"/>
-    <row r="110" ht="15.75" customHeight="1" s="21"/>
-    <row r="111" ht="15.75" customHeight="1" s="21"/>
-    <row r="112" ht="15.75" customHeight="1" s="21"/>
-    <row r="113" ht="15.75" customHeight="1" s="21"/>
-    <row r="114" ht="15.75" customHeight="1" s="21"/>
-    <row r="115" ht="15.75" customHeight="1" s="21"/>
-    <row r="116" ht="15.75" customHeight="1" s="21"/>
-    <row r="117" ht="15.75" customHeight="1" s="21"/>
-    <row r="118" ht="15.75" customHeight="1" s="21"/>
-    <row r="119" ht="15.75" customHeight="1" s="21"/>
-    <row r="120" ht="15.75" customHeight="1" s="21"/>
-    <row r="121" ht="15.75" customHeight="1" s="21"/>
-    <row r="122" ht="15.75" customHeight="1" s="21"/>
-    <row r="123" ht="15.75" customHeight="1" s="21"/>
-    <row r="124" ht="15.75" customHeight="1" s="21"/>
-    <row r="125" ht="15.75" customHeight="1" s="21"/>
-    <row r="126" ht="15.75" customHeight="1" s="21"/>
-    <row r="127" ht="15.75" customHeight="1" s="21"/>
-    <row r="128" ht="15.75" customHeight="1" s="21"/>
-    <row r="129" ht="15.75" customHeight="1" s="21"/>
-    <row r="130" ht="15.75" customHeight="1" s="21"/>
-    <row r="131" ht="15.75" customHeight="1" s="21"/>
-    <row r="132" ht="15.75" customHeight="1" s="21"/>
-    <row r="133" ht="15.75" customHeight="1" s="21"/>
-    <row r="134" ht="15.75" customHeight="1" s="21"/>
-    <row r="135" ht="15.75" customHeight="1" s="21"/>
-    <row r="136" ht="15.75" customHeight="1" s="21"/>
-    <row r="137" ht="15.75" customHeight="1" s="21"/>
-    <row r="138" ht="15.75" customHeight="1" s="21"/>
-    <row r="139" ht="15.75" customHeight="1" s="21"/>
-    <row r="140" ht="15.75" customHeight="1" s="21"/>
-    <row r="141" ht="15.75" customHeight="1" s="21"/>
-    <row r="142" ht="15.75" customHeight="1" s="21"/>
-    <row r="143" ht="15.75" customHeight="1" s="21"/>
-    <row r="144" ht="15.75" customHeight="1" s="21"/>
-    <row r="145" ht="15.75" customHeight="1" s="21"/>
-    <row r="146" ht="15.75" customHeight="1" s="21"/>
-    <row r="147" ht="15.75" customHeight="1" s="21"/>
-    <row r="148" ht="15.75" customHeight="1" s="21"/>
-    <row r="149" ht="15.75" customHeight="1" s="21"/>
-    <row r="150" ht="15.75" customHeight="1" s="21"/>
-    <row r="151" ht="15.75" customHeight="1" s="21"/>
-    <row r="152" ht="15.75" customHeight="1" s="21"/>
-    <row r="153" ht="15.75" customHeight="1" s="21"/>
-    <row r="154" ht="15.75" customHeight="1" s="21"/>
-    <row r="155" ht="15.75" customHeight="1" s="21"/>
-    <row r="156" ht="15.75" customHeight="1" s="21"/>
-    <row r="157" ht="15.75" customHeight="1" s="21"/>
-    <row r="158" ht="15.75" customHeight="1" s="21"/>
-    <row r="159" ht="15.75" customHeight="1" s="21"/>
-    <row r="160" ht="15.75" customHeight="1" s="21"/>
-    <row r="161" ht="15.75" customHeight="1" s="21"/>
-    <row r="162" ht="15.75" customHeight="1" s="21"/>
-    <row r="163" ht="15.75" customHeight="1" s="21"/>
-    <row r="164" ht="15.75" customHeight="1" s="21"/>
-    <row r="165" ht="15.75" customHeight="1" s="21"/>
-    <row r="166" ht="15.75" customHeight="1" s="21"/>
-    <row r="167" ht="15.75" customHeight="1" s="21"/>
-    <row r="168" ht="15.75" customHeight="1" s="21"/>
-    <row r="169" ht="15.75" customHeight="1" s="21"/>
-    <row r="170" ht="15.75" customHeight="1" s="21"/>
-    <row r="171" ht="15.75" customHeight="1" s="21"/>
-    <row r="172" ht="15.75" customHeight="1" s="21"/>
-    <row r="173" ht="15.75" customHeight="1" s="21"/>
-    <row r="174" ht="15.75" customHeight="1" s="21"/>
-    <row r="175" ht="15.75" customHeight="1" s="21"/>
-    <row r="176" ht="15.75" customHeight="1" s="21"/>
-    <row r="177" ht="15.75" customHeight="1" s="21"/>
-    <row r="178" ht="15.75" customHeight="1" s="21"/>
-    <row r="179" ht="15.75" customHeight="1" s="21"/>
-    <row r="180" ht="15.75" customHeight="1" s="21"/>
-    <row r="181" ht="15.75" customHeight="1" s="21"/>
-    <row r="182" ht="15.75" customHeight="1" s="21"/>
-    <row r="183" ht="15.75" customHeight="1" s="21"/>
-    <row r="184" ht="15.75" customHeight="1" s="21"/>
-    <row r="185" ht="15.75" customHeight="1" s="21"/>
-    <row r="186" ht="15.75" customHeight="1" s="21"/>
-    <row r="187" ht="15.75" customHeight="1" s="21"/>
-    <row r="188" ht="15.75" customHeight="1" s="21"/>
-    <row r="189" ht="15.75" customHeight="1" s="21"/>
-    <row r="190" ht="15.75" customHeight="1" s="21"/>
-    <row r="191" ht="15.75" customHeight="1" s="21"/>
-    <row r="192" ht="15.75" customHeight="1" s="21"/>
-    <row r="193" ht="15.75" customHeight="1" s="21"/>
-    <row r="194" ht="15.75" customHeight="1" s="21"/>
-    <row r="195" ht="15.75" customHeight="1" s="21"/>
-    <row r="196" ht="15.75" customHeight="1" s="21"/>
-    <row r="197" ht="15.75" customHeight="1" s="21"/>
-    <row r="198" ht="15.75" customHeight="1" s="21"/>
-    <row r="199" ht="15.75" customHeight="1" s="21"/>
-    <row r="200" ht="15.75" customHeight="1" s="21"/>
-    <row r="201" ht="15.75" customHeight="1" s="21"/>
-    <row r="202" ht="15.75" customHeight="1" s="21"/>
-    <row r="203" ht="15.75" customHeight="1" s="21"/>
-    <row r="204" ht="15.75" customHeight="1" s="21"/>
-    <row r="205" ht="15.75" customHeight="1" s="21"/>
-    <row r="206" ht="15.75" customHeight="1" s="21"/>
-    <row r="207" ht="15.75" customHeight="1" s="21"/>
-    <row r="208" ht="15.75" customHeight="1" s="21"/>
-    <row r="209" ht="15.75" customHeight="1" s="21"/>
-    <row r="210" ht="15.75" customHeight="1" s="21"/>
-    <row r="211" ht="15.75" customHeight="1" s="21"/>
-    <row r="212" ht="15.75" customHeight="1" s="21"/>
-    <row r="213" ht="15.75" customHeight="1" s="21"/>
-    <row r="214" ht="15.75" customHeight="1" s="21"/>
-    <row r="215" ht="15.75" customHeight="1" s="21"/>
-    <row r="216" ht="15.75" customHeight="1" s="21"/>
-    <row r="217" ht="15.75" customHeight="1" s="21"/>
-    <row r="218" ht="15.75" customHeight="1" s="21"/>
-    <row r="219" ht="15.75" customHeight="1" s="21"/>
-    <row r="220" ht="15.75" customHeight="1" s="21"/>
-    <row r="221" ht="15.75" customHeight="1" s="21"/>
-    <row r="222" ht="15.75" customHeight="1" s="21"/>
-    <row r="223" ht="15.75" customHeight="1" s="21"/>
-    <row r="224" ht="15.75" customHeight="1" s="21"/>
-    <row r="225" ht="15.75" customHeight="1" s="21"/>
-    <row r="226" ht="15.75" customHeight="1" s="21"/>
-    <row r="227" ht="15.75" customHeight="1" s="21"/>
-    <row r="228" ht="15.75" customHeight="1" s="21"/>
-    <row r="229" ht="15.75" customHeight="1" s="21"/>
-    <row r="230" ht="15.75" customHeight="1" s="21"/>
-    <row r="231" ht="15.75" customHeight="1" s="21"/>
-    <row r="232" ht="15.75" customHeight="1" s="21"/>
-    <row r="233" ht="15.75" customHeight="1" s="21"/>
-    <row r="234" ht="15.75" customHeight="1" s="21"/>
-    <row r="235" ht="15.75" customHeight="1" s="21"/>
-    <row r="236" ht="15.75" customHeight="1" s="21"/>
-    <row r="237" ht="15.75" customHeight="1" s="21"/>
-    <row r="238" ht="15.75" customHeight="1" s="21"/>
-    <row r="239" ht="15.75" customHeight="1" s="21"/>
-    <row r="240" ht="15.75" customHeight="1" s="21"/>
-    <row r="241" ht="15.75" customHeight="1" s="21"/>
-    <row r="242" ht="15.75" customHeight="1" s="21"/>
-    <row r="243" ht="15.75" customHeight="1" s="21"/>
-    <row r="244" ht="15.75" customHeight="1" s="21"/>
-    <row r="245" ht="15.75" customHeight="1" s="21"/>
-    <row r="246" ht="15.75" customHeight="1" s="21"/>
-    <row r="247" ht="15.75" customHeight="1" s="21"/>
-    <row r="248" ht="15.75" customHeight="1" s="21"/>
-    <row r="249" ht="15.75" customHeight="1" s="21"/>
-    <row r="250" ht="15.75" customHeight="1" s="21"/>
-    <row r="251" ht="15.75" customHeight="1" s="21"/>
-    <row r="252" ht="15.75" customHeight="1" s="21"/>
-    <row r="253" ht="15.75" customHeight="1" s="21"/>
-    <row r="254" ht="15.75" customHeight="1" s="21"/>
-    <row r="255" ht="15.75" customHeight="1" s="21"/>
-    <row r="256" ht="15.75" customHeight="1" s="21"/>
-    <row r="257" ht="15.75" customHeight="1" s="21"/>
-    <row r="258" ht="15.75" customHeight="1" s="21"/>
-    <row r="259" ht="15.75" customHeight="1" s="21"/>
-    <row r="260" ht="15.75" customHeight="1" s="21"/>
-    <row r="261" ht="15.75" customHeight="1" s="21"/>
-    <row r="262" ht="15.75" customHeight="1" s="21"/>
-    <row r="263" ht="15.75" customHeight="1" s="21"/>
-    <row r="264" ht="15.75" customHeight="1" s="21"/>
-    <row r="265" ht="15.75" customHeight="1" s="21"/>
-    <row r="266" ht="15.75" customHeight="1" s="21"/>
-    <row r="267" ht="15.75" customHeight="1" s="21"/>
-    <row r="268" ht="15.75" customHeight="1" s="21"/>
-    <row r="269" ht="15.75" customHeight="1" s="21"/>
-    <row r="270" ht="15.75" customHeight="1" s="21"/>
-    <row r="271" ht="15.75" customHeight="1" s="21"/>
-    <row r="272" ht="15.75" customHeight="1" s="21"/>
-    <row r="273" ht="15.75" customHeight="1" s="21"/>
-    <row r="274" ht="15.75" customHeight="1" s="21"/>
-    <row r="275" ht="15.75" customHeight="1" s="21"/>
-    <row r="276" ht="15.75" customHeight="1" s="21"/>
-    <row r="277" ht="15.75" customHeight="1" s="21"/>
-    <row r="278" ht="15.75" customHeight="1" s="21"/>
-    <row r="279" ht="15.75" customHeight="1" s="21"/>
-    <row r="280" ht="15.75" customHeight="1" s="21"/>
-    <row r="281" ht="15.75" customHeight="1" s="21"/>
-    <row r="282" ht="15.75" customHeight="1" s="21"/>
-    <row r="283" ht="15.75" customHeight="1" s="21"/>
-    <row r="284" ht="15.75" customHeight="1" s="21"/>
-    <row r="285" ht="15.75" customHeight="1" s="21"/>
-    <row r="286" ht="15.75" customHeight="1" s="21"/>
-    <row r="287" ht="15.75" customHeight="1" s="21"/>
-    <row r="288" ht="15.75" customHeight="1" s="21"/>
-    <row r="289" ht="15.75" customHeight="1" s="21"/>
-    <row r="290" ht="15.75" customHeight="1" s="21"/>
-    <row r="291" ht="15.75" customHeight="1" s="21"/>
-    <row r="292" ht="15.75" customHeight="1" s="21"/>
-    <row r="293" ht="15.75" customHeight="1" s="21"/>
-    <row r="294" ht="15.75" customHeight="1" s="21"/>
-    <row r="295" ht="15.75" customHeight="1" s="21"/>
-    <row r="296" ht="15.75" customHeight="1" s="21"/>
-    <row r="297" ht="15.75" customHeight="1" s="21"/>
-    <row r="298" ht="15.75" customHeight="1" s="21"/>
-    <row r="299" ht="15.75" customHeight="1" s="21"/>
-    <row r="300" ht="15.75" customHeight="1" s="21"/>
-    <row r="301" ht="15.75" customHeight="1" s="21"/>
-    <row r="302" ht="15.75" customHeight="1" s="21"/>
-    <row r="303" ht="15.75" customHeight="1" s="21"/>
-    <row r="304" ht="15.75" customHeight="1" s="21"/>
-    <row r="305" ht="15.75" customHeight="1" s="21"/>
-    <row r="306" ht="15.75" customHeight="1" s="21"/>
-    <row r="307" ht="15.75" customHeight="1" s="21"/>
-    <row r="308" ht="15.75" customHeight="1" s="21"/>
-    <row r="309" ht="15.75" customHeight="1" s="21"/>
-    <row r="310" ht="15.75" customHeight="1" s="21"/>
-    <row r="311" ht="15.75" customHeight="1" s="21"/>
-    <row r="312" ht="15.75" customHeight="1" s="21"/>
-    <row r="313" ht="15.75" customHeight="1" s="21"/>
-    <row r="314" ht="15.75" customHeight="1" s="21"/>
-    <row r="315" ht="15.75" customHeight="1" s="21"/>
-    <row r="316" ht="15.75" customHeight="1" s="21"/>
-    <row r="317" ht="15.75" customHeight="1" s="21"/>
-    <row r="318" ht="15.75" customHeight="1" s="21"/>
-    <row r="319" ht="15.75" customHeight="1" s="21"/>
-    <row r="320" ht="15.75" customHeight="1" s="21"/>
-    <row r="321" ht="15.75" customHeight="1" s="21"/>
-    <row r="322" ht="15.75" customHeight="1" s="21"/>
-    <row r="323" ht="15.75" customHeight="1" s="21"/>
-    <row r="324" ht="15.75" customHeight="1" s="21"/>
-    <row r="325" ht="15.75" customHeight="1" s="21"/>
-    <row r="326" ht="15.75" customHeight="1" s="21"/>
-    <row r="327" ht="15.75" customHeight="1" s="21"/>
-    <row r="328" ht="15.75" customHeight="1" s="21"/>
-    <row r="329" ht="15.75" customHeight="1" s="21"/>
-    <row r="330" ht="15.75" customHeight="1" s="21"/>
-    <row r="331" ht="15.75" customHeight="1" s="21"/>
-    <row r="332" ht="15.75" customHeight="1" s="21"/>
-    <row r="333" ht="15.75" customHeight="1" s="21"/>
-    <row r="334" ht="15.75" customHeight="1" s="21"/>
-    <row r="335" ht="15.75" customHeight="1" s="21"/>
-    <row r="336" ht="15.75" customHeight="1" s="21"/>
-    <row r="337" ht="15.75" customHeight="1" s="21"/>
-    <row r="338" ht="15.75" customHeight="1" s="21"/>
-    <row r="339" ht="15.75" customHeight="1" s="21"/>
-    <row r="340" ht="15.75" customHeight="1" s="21"/>
-    <row r="341" ht="15.75" customHeight="1" s="21"/>
-    <row r="342" ht="15.75" customHeight="1" s="21"/>
-    <row r="343" ht="15.75" customHeight="1" s="21"/>
-    <row r="344" ht="15.75" customHeight="1" s="21"/>
-    <row r="345" ht="15.75" customHeight="1" s="21"/>
-    <row r="346" ht="15.75" customHeight="1" s="21"/>
-    <row r="347" ht="15.75" customHeight="1" s="21"/>
-    <row r="348" ht="15.75" customHeight="1" s="21"/>
-    <row r="349" ht="15.75" customHeight="1" s="21"/>
-    <row r="350" ht="15.75" customHeight="1" s="21"/>
-    <row r="351" ht="15.75" customHeight="1" s="21"/>
-    <row r="352" ht="15.75" customHeight="1" s="21"/>
-    <row r="353" ht="15.75" customHeight="1" s="21"/>
-    <row r="354" ht="15.75" customHeight="1" s="21"/>
-    <row r="355" ht="15.75" customHeight="1" s="21"/>
-    <row r="356" ht="15.75" customHeight="1" s="21"/>
-    <row r="357" ht="15.75" customHeight="1" s="21"/>
-    <row r="358" ht="15.75" customHeight="1" s="21"/>
-    <row r="359" ht="15.75" customHeight="1" s="21"/>
-    <row r="360" ht="15.75" customHeight="1" s="21"/>
-    <row r="361" ht="15.75" customHeight="1" s="21"/>
-    <row r="362" ht="15.75" customHeight="1" s="21"/>
-    <row r="363" ht="15.75" customHeight="1" s="21"/>
-    <row r="364" ht="15.75" customHeight="1" s="21"/>
-    <row r="365" ht="15.75" customHeight="1" s="21"/>
-    <row r="366" ht="15.75" customHeight="1" s="21"/>
-    <row r="367" ht="15.75" customHeight="1" s="21"/>
-    <row r="368" ht="15.75" customHeight="1" s="21"/>
-    <row r="369" ht="15.75" customHeight="1" s="21"/>
-    <row r="370" ht="15.75" customHeight="1" s="21"/>
-    <row r="371" ht="15.75" customHeight="1" s="21"/>
-    <row r="372" ht="15.75" customHeight="1" s="21"/>
-    <row r="373" ht="15.75" customHeight="1" s="21"/>
-    <row r="374" ht="15.75" customHeight="1" s="21"/>
-    <row r="375" ht="15.75" customHeight="1" s="21"/>
-    <row r="376" ht="15.75" customHeight="1" s="21"/>
-    <row r="377" ht="15.75" customHeight="1" s="21"/>
-    <row r="378" ht="15.75" customHeight="1" s="21"/>
-    <row r="379" ht="15.75" customHeight="1" s="21"/>
-    <row r="380" ht="15.75" customHeight="1" s="21"/>
-    <row r="381" ht="15.75" customHeight="1" s="21"/>
-    <row r="382" ht="15.75" customHeight="1" s="21"/>
-    <row r="383" ht="15.75" customHeight="1" s="21"/>
-    <row r="384" ht="15.75" customHeight="1" s="21"/>
-    <row r="385" ht="15.75" customHeight="1" s="21"/>
-    <row r="386" ht="15.75" customHeight="1" s="21"/>
-    <row r="387" ht="15.75" customHeight="1" s="21"/>
-    <row r="388" ht="15.75" customHeight="1" s="21"/>
-    <row r="389" ht="15.75" customHeight="1" s="21"/>
-    <row r="390" ht="15.75" customHeight="1" s="21"/>
-    <row r="391" ht="15.75" customHeight="1" s="21"/>
-    <row r="392" ht="15.75" customHeight="1" s="21"/>
-    <row r="393" ht="15.75" customHeight="1" s="21"/>
-    <row r="394" ht="15.75" customHeight="1" s="21"/>
-    <row r="395" ht="15.75" customHeight="1" s="21"/>
-    <row r="396" ht="15.75" customHeight="1" s="21"/>
-    <row r="397" ht="15.75" customHeight="1" s="21"/>
-    <row r="398" ht="15.75" customHeight="1" s="21"/>
-    <row r="399" ht="15.75" customHeight="1" s="21"/>
-    <row r="400" ht="15.75" customHeight="1" s="21"/>
-    <row r="401" ht="15.75" customHeight="1" s="21"/>
-    <row r="402" ht="15.75" customHeight="1" s="21"/>
-    <row r="403" ht="15.75" customHeight="1" s="21"/>
-    <row r="404" ht="15.75" customHeight="1" s="21"/>
-    <row r="405" ht="15.75" customHeight="1" s="21"/>
-    <row r="406" ht="15.75" customHeight="1" s="21"/>
-    <row r="407" ht="15.75" customHeight="1" s="21"/>
-    <row r="408" ht="15.75" customHeight="1" s="21"/>
-    <row r="409" ht="15.75" customHeight="1" s="21"/>
-    <row r="410" ht="15.75" customHeight="1" s="21"/>
-    <row r="411" ht="15.75" customHeight="1" s="21"/>
-    <row r="412" ht="15.75" customHeight="1" s="21"/>
-    <row r="413" ht="15.75" customHeight="1" s="21"/>
-    <row r="414" ht="15.75" customHeight="1" s="21"/>
-    <row r="415" ht="15.75" customHeight="1" s="21"/>
-    <row r="416" ht="15.75" customHeight="1" s="21"/>
-    <row r="417" ht="15.75" customHeight="1" s="21"/>
-    <row r="418" ht="15.75" customHeight="1" s="21"/>
-    <row r="419" ht="15.75" customHeight="1" s="21"/>
-    <row r="420" ht="15.75" customHeight="1" s="21"/>
-    <row r="421" ht="15.75" customHeight="1" s="21"/>
-    <row r="422" ht="15.75" customHeight="1" s="21"/>
-    <row r="423" ht="15.75" customHeight="1" s="21"/>
-    <row r="424" ht="15.75" customHeight="1" s="21"/>
-    <row r="425" ht="15.75" customHeight="1" s="21"/>
-    <row r="426" ht="15.75" customHeight="1" s="21"/>
-    <row r="427" ht="15.75" customHeight="1" s="21"/>
-    <row r="428" ht="15.75" customHeight="1" s="21"/>
-    <row r="429" ht="15.75" customHeight="1" s="21"/>
-    <row r="430" ht="15.75" customHeight="1" s="21"/>
-    <row r="431" ht="15.75" customHeight="1" s="21"/>
-    <row r="432" ht="15.75" customHeight="1" s="21"/>
-    <row r="433" ht="15.75" customHeight="1" s="21"/>
-    <row r="434" ht="15.75" customHeight="1" s="21"/>
-    <row r="435" ht="15.75" customHeight="1" s="21"/>
-    <row r="436" ht="15.75" customHeight="1" s="21"/>
-    <row r="437" ht="15.75" customHeight="1" s="21"/>
-    <row r="438" ht="15.75" customHeight="1" s="21"/>
-    <row r="439" ht="15.75" customHeight="1" s="21"/>
-    <row r="440" ht="15.75" customHeight="1" s="21"/>
-    <row r="441" ht="15.75" customHeight="1" s="21"/>
-    <row r="442" ht="15.75" customHeight="1" s="21"/>
-    <row r="443" ht="15.75" customHeight="1" s="21"/>
-    <row r="444" ht="15.75" customHeight="1" s="21"/>
-    <row r="445" ht="15.75" customHeight="1" s="21"/>
-    <row r="446" ht="15.75" customHeight="1" s="21"/>
-    <row r="447" ht="15.75" customHeight="1" s="21"/>
-    <row r="448" ht="15.75" customHeight="1" s="21"/>
-    <row r="449" ht="15.75" customHeight="1" s="21"/>
-    <row r="450" ht="15.75" customHeight="1" s="21"/>
-    <row r="451" ht="15.75" customHeight="1" s="21"/>
-    <row r="452" ht="15.75" customHeight="1" s="21"/>
-    <row r="453" ht="15.75" customHeight="1" s="21"/>
-    <row r="454" ht="15.75" customHeight="1" s="21"/>
-    <row r="455" ht="15.75" customHeight="1" s="21"/>
-    <row r="456" ht="15.75" customHeight="1" s="21"/>
-    <row r="457" ht="15.75" customHeight="1" s="21"/>
-    <row r="458" ht="15.75" customHeight="1" s="21"/>
-    <row r="459" ht="15.75" customHeight="1" s="21"/>
-    <row r="460" ht="15.75" customHeight="1" s="21"/>
-    <row r="461" ht="15.75" customHeight="1" s="21"/>
-    <row r="462" ht="15.75" customHeight="1" s="21"/>
-    <row r="463" ht="15.75" customHeight="1" s="21"/>
-    <row r="464" ht="15.75" customHeight="1" s="21"/>
-    <row r="465" ht="15.75" customHeight="1" s="21"/>
-    <row r="466" ht="15.75" customHeight="1" s="21"/>
-    <row r="467" ht="15.75" customHeight="1" s="21"/>
-    <row r="468" ht="15.75" customHeight="1" s="21"/>
-    <row r="469" ht="15.75" customHeight="1" s="21"/>
-    <row r="470" ht="15.75" customHeight="1" s="21"/>
-    <row r="471" ht="15.75" customHeight="1" s="21"/>
-    <row r="472" ht="15.75" customHeight="1" s="21"/>
-    <row r="473" ht="15.75" customHeight="1" s="21"/>
-    <row r="474" ht="15.75" customHeight="1" s="21"/>
-    <row r="475" ht="15.75" customHeight="1" s="21"/>
-    <row r="476" ht="15.75" customHeight="1" s="21"/>
-    <row r="477" ht="15.75" customHeight="1" s="21"/>
-    <row r="478" ht="15.75" customHeight="1" s="21"/>
-    <row r="479" ht="15.75" customHeight="1" s="21"/>
-    <row r="480" ht="15.75" customHeight="1" s="21"/>
-    <row r="481" ht="15.75" customHeight="1" s="21"/>
-    <row r="482" ht="15.75" customHeight="1" s="21"/>
-    <row r="483" ht="15.75" customHeight="1" s="21"/>
-    <row r="484" ht="15.75" customHeight="1" s="21"/>
-    <row r="485" ht="15.75" customHeight="1" s="21"/>
-    <row r="486" ht="15.75" customHeight="1" s="21"/>
-    <row r="487" ht="15.75" customHeight="1" s="21"/>
-    <row r="488" ht="15.75" customHeight="1" s="21"/>
-    <row r="489" ht="15.75" customHeight="1" s="21"/>
-    <row r="490" ht="15.75" customHeight="1" s="21"/>
-    <row r="491" ht="15.75" customHeight="1" s="21"/>
-    <row r="492" ht="15.75" customHeight="1" s="21"/>
-    <row r="493" ht="15.75" customHeight="1" s="21"/>
-    <row r="494" ht="15.75" customHeight="1" s="21"/>
-    <row r="495" ht="15.75" customHeight="1" s="21"/>
-    <row r="496" ht="15.75" customHeight="1" s="21"/>
-    <row r="497" ht="15.75" customHeight="1" s="21"/>
-    <row r="498" ht="15.75" customHeight="1" s="21"/>
-    <row r="499" ht="15.75" customHeight="1" s="21"/>
-    <row r="500" ht="15.75" customHeight="1" s="21"/>
-    <row r="501" ht="15.75" customHeight="1" s="21"/>
-    <row r="502" ht="15.75" customHeight="1" s="21"/>
-    <row r="503" ht="15.75" customHeight="1" s="21"/>
-    <row r="504" ht="15.75" customHeight="1" s="21"/>
-    <row r="505" ht="15.75" customHeight="1" s="21"/>
-    <row r="506" ht="15.75" customHeight="1" s="21"/>
-    <row r="507" ht="15.75" customHeight="1" s="21"/>
-    <row r="508" ht="15.75" customHeight="1" s="21"/>
-    <row r="509" ht="15.75" customHeight="1" s="21"/>
-    <row r="510" ht="15.75" customHeight="1" s="21"/>
-    <row r="511" ht="15.75" customHeight="1" s="21"/>
-    <row r="512" ht="15.75" customHeight="1" s="21"/>
-    <row r="513" ht="15.75" customHeight="1" s="21"/>
-    <row r="514" ht="15.75" customHeight="1" s="21"/>
-    <row r="515" ht="15.75" customHeight="1" s="21"/>
-    <row r="516" ht="15.75" customHeight="1" s="21"/>
-    <row r="517" ht="15.75" customHeight="1" s="21"/>
-    <row r="518" ht="15.75" customHeight="1" s="21"/>
-    <row r="519" ht="15.75" customHeight="1" s="21"/>
-    <row r="520" ht="15.75" customHeight="1" s="21"/>
-    <row r="521" ht="15.75" customHeight="1" s="21"/>
-    <row r="522" ht="15.75" customHeight="1" s="21"/>
-    <row r="523" ht="15.75" customHeight="1" s="21"/>
-    <row r="524" ht="15.75" customHeight="1" s="21"/>
-    <row r="525" ht="15.75" customHeight="1" s="21"/>
-    <row r="526" ht="15.75" customHeight="1" s="21"/>
-    <row r="527" ht="15.75" customHeight="1" s="21"/>
-    <row r="528" ht="15.75" customHeight="1" s="21"/>
-    <row r="529" ht="15.75" customHeight="1" s="21"/>
-    <row r="530" ht="15.75" customHeight="1" s="21"/>
-    <row r="531" ht="15.75" customHeight="1" s="21"/>
-    <row r="532" ht="15.75" customHeight="1" s="21"/>
-    <row r="533" ht="15.75" customHeight="1" s="21"/>
-    <row r="534" ht="15.75" customHeight="1" s="21"/>
-    <row r="535" ht="15.75" customHeight="1" s="21"/>
-    <row r="536" ht="15.75" customHeight="1" s="21"/>
-    <row r="537" ht="15.75" customHeight="1" s="21"/>
-    <row r="538" ht="15.75" customHeight="1" s="21"/>
-    <row r="539" ht="15.75" customHeight="1" s="21"/>
-    <row r="540" ht="15.75" customHeight="1" s="21"/>
-    <row r="541" ht="15.75" customHeight="1" s="21"/>
-    <row r="542" ht="15.75" customHeight="1" s="21"/>
-    <row r="543" ht="15.75" customHeight="1" s="21"/>
-    <row r="544" ht="15.75" customHeight="1" s="21"/>
-    <row r="545" ht="15.75" customHeight="1" s="21"/>
-    <row r="546" ht="15.75" customHeight="1" s="21"/>
-    <row r="547" ht="15.75" customHeight="1" s="21"/>
-    <row r="548" ht="15.75" customHeight="1" s="21"/>
-    <row r="549" ht="15.75" customHeight="1" s="21"/>
-    <row r="550" ht="15.75" customHeight="1" s="21"/>
-    <row r="551" ht="15.75" customHeight="1" s="21"/>
-    <row r="552" ht="15.75" customHeight="1" s="21"/>
-    <row r="553" ht="15.75" customHeight="1" s="21"/>
-    <row r="554" ht="15.75" customHeight="1" s="21"/>
-    <row r="555" ht="15.75" customHeight="1" s="21"/>
-    <row r="556" ht="15.75" customHeight="1" s="21"/>
-    <row r="557" ht="15.75" customHeight="1" s="21"/>
-    <row r="558" ht="15.75" customHeight="1" s="21"/>
-    <row r="559" ht="15.75" customHeight="1" s="21"/>
-    <row r="560" ht="15.75" customHeight="1" s="21"/>
-    <row r="561" ht="15.75" customHeight="1" s="21"/>
-    <row r="562" ht="15.75" customHeight="1" s="21"/>
-    <row r="563" ht="15.75" customHeight="1" s="21"/>
-    <row r="564" ht="15.75" customHeight="1" s="21"/>
-    <row r="565" ht="15.75" customHeight="1" s="21"/>
-    <row r="566" ht="15.75" customHeight="1" s="21"/>
-    <row r="567" ht="15.75" customHeight="1" s="21"/>
-    <row r="568" ht="15.75" customHeight="1" s="21"/>
-    <row r="569" ht="15.75" customHeight="1" s="21"/>
-    <row r="570" ht="15.75" customHeight="1" s="21"/>
-    <row r="571" ht="15.75" customHeight="1" s="21"/>
-    <row r="572" ht="15.75" customHeight="1" s="21"/>
-    <row r="573" ht="15.75" customHeight="1" s="21"/>
-    <row r="574" ht="15.75" customHeight="1" s="21"/>
-    <row r="575" ht="15.75" customHeight="1" s="21"/>
-    <row r="576" ht="15.75" customHeight="1" s="21"/>
-    <row r="577" ht="15.75" customHeight="1" s="21"/>
-    <row r="578" ht="15.75" customHeight="1" s="21"/>
-    <row r="579" ht="15.75" customHeight="1" s="21"/>
-    <row r="580" ht="15.75" customHeight="1" s="21"/>
-    <row r="581" ht="15.75" customHeight="1" s="21"/>
-    <row r="582" ht="15.75" customHeight="1" s="21"/>
-    <row r="583" ht="15.75" customHeight="1" s="21"/>
-    <row r="584" ht="15.75" customHeight="1" s="21"/>
-    <row r="585" ht="15.75" customHeight="1" s="21"/>
-    <row r="586" ht="15.75" customHeight="1" s="21"/>
-    <row r="587" ht="15.75" customHeight="1" s="21"/>
-    <row r="588" ht="15.75" customHeight="1" s="21"/>
-    <row r="589" ht="15.75" customHeight="1" s="21"/>
-    <row r="590" ht="15.75" customHeight="1" s="21"/>
-    <row r="591" ht="15.75" customHeight="1" s="21"/>
-    <row r="592" ht="15.75" customHeight="1" s="21"/>
-    <row r="593" ht="15.75" customHeight="1" s="21"/>
-    <row r="594" ht="15.75" customHeight="1" s="21"/>
-    <row r="595" ht="15.75" customHeight="1" s="21"/>
-    <row r="596" ht="15.75" customHeight="1" s="21"/>
-    <row r="597" ht="15.75" customHeight="1" s="21"/>
-    <row r="598" ht="15.75" customHeight="1" s="21"/>
-    <row r="599" ht="15.75" customHeight="1" s="21"/>
-    <row r="600" ht="15.75" customHeight="1" s="21"/>
-    <row r="601" ht="15.75" customHeight="1" s="21"/>
-    <row r="602" ht="15.75" customHeight="1" s="21"/>
-    <row r="603" ht="15.75" customHeight="1" s="21"/>
-    <row r="604" ht="15.75" customHeight="1" s="21"/>
-    <row r="605" ht="15.75" customHeight="1" s="21"/>
-    <row r="606" ht="15.75" customHeight="1" s="21"/>
-    <row r="607" ht="15.75" customHeight="1" s="21"/>
-    <row r="608" ht="15.75" customHeight="1" s="21"/>
-    <row r="609" ht="15.75" customHeight="1" s="21"/>
-    <row r="610" ht="15.75" customHeight="1" s="21"/>
-    <row r="611" ht="15.75" customHeight="1" s="21"/>
-    <row r="612" ht="15.75" customHeight="1" s="21"/>
-    <row r="613" ht="15.75" customHeight="1" s="21"/>
-    <row r="614" ht="15.75" customHeight="1" s="21"/>
-    <row r="615" ht="15.75" customHeight="1" s="21"/>
-    <row r="616" ht="15.75" customHeight="1" s="21"/>
-    <row r="617" ht="15.75" customHeight="1" s="21"/>
-    <row r="618" ht="15.75" customHeight="1" s="21"/>
-    <row r="619" ht="15.75" customHeight="1" s="21"/>
-    <row r="620" ht="15.75" customHeight="1" s="21"/>
-    <row r="621" ht="15.75" customHeight="1" s="21"/>
-    <row r="622" ht="15.75" customHeight="1" s="21"/>
-    <row r="623" ht="15.75" customHeight="1" s="21"/>
-    <row r="624" ht="15.75" customHeight="1" s="21"/>
-    <row r="625" ht="15.75" customHeight="1" s="21"/>
-    <row r="626" ht="15.75" customHeight="1" s="21"/>
-    <row r="627" ht="15.75" customHeight="1" s="21"/>
-    <row r="628" ht="15.75" customHeight="1" s="21"/>
-    <row r="629" ht="15.75" customHeight="1" s="21"/>
-    <row r="630" ht="15.75" customHeight="1" s="21"/>
-    <row r="631" ht="15.75" customHeight="1" s="21"/>
-    <row r="632" ht="15.75" customHeight="1" s="21"/>
-    <row r="633" ht="15.75" customHeight="1" s="21"/>
-    <row r="634" ht="15.75" customHeight="1" s="21"/>
-    <row r="635" ht="15.75" customHeight="1" s="21"/>
-    <row r="636" ht="15.75" customHeight="1" s="21"/>
-    <row r="637" ht="15.75" customHeight="1" s="21"/>
-    <row r="638" ht="15.75" customHeight="1" s="21"/>
-    <row r="639" ht="15.75" customHeight="1" s="21"/>
-    <row r="640" ht="15.75" customHeight="1" s="21"/>
-    <row r="641" ht="15.75" customHeight="1" s="21"/>
-    <row r="642" ht="15.75" customHeight="1" s="21"/>
-    <row r="643" ht="15.75" customHeight="1" s="21"/>
-    <row r="644" ht="15.75" customHeight="1" s="21"/>
-    <row r="645" ht="15.75" customHeight="1" s="21"/>
-    <row r="646" ht="15.75" customHeight="1" s="21"/>
-    <row r="647" ht="15.75" customHeight="1" s="21"/>
-    <row r="648" ht="15.75" customHeight="1" s="21"/>
-    <row r="649" ht="15.75" customHeight="1" s="21"/>
-    <row r="650" ht="15.75" customHeight="1" s="21"/>
-    <row r="651" ht="15.75" customHeight="1" s="21"/>
-    <row r="652" ht="15.75" customHeight="1" s="21"/>
-    <row r="653" ht="15.75" customHeight="1" s="21"/>
-    <row r="654" ht="15.75" customHeight="1" s="21"/>
-    <row r="655" ht="15.75" customHeight="1" s="21"/>
-    <row r="656" ht="15.75" customHeight="1" s="21"/>
-    <row r="657" ht="15.75" customHeight="1" s="21"/>
-    <row r="658" ht="15.75" customHeight="1" s="21"/>
-    <row r="659" ht="15.75" customHeight="1" s="21"/>
-    <row r="660" ht="15.75" customHeight="1" s="21"/>
-    <row r="661" ht="15.75" customHeight="1" s="21"/>
-    <row r="662" ht="15.75" customHeight="1" s="21"/>
-    <row r="663" ht="15.75" customHeight="1" s="21"/>
-    <row r="664" ht="15.75" customHeight="1" s="21"/>
-    <row r="665" ht="15.75" customHeight="1" s="21"/>
-    <row r="666" ht="15.75" customHeight="1" s="21"/>
-    <row r="667" ht="15.75" customHeight="1" s="21"/>
-    <row r="668" ht="15.75" customHeight="1" s="21"/>
-    <row r="669" ht="15.75" customHeight="1" s="21"/>
-    <row r="670" ht="15.75" customHeight="1" s="21"/>
-    <row r="671" ht="15.75" customHeight="1" s="21"/>
-    <row r="672" ht="15.75" customHeight="1" s="21"/>
-    <row r="673" ht="15.75" customHeight="1" s="21"/>
-    <row r="674" ht="15.75" customHeight="1" s="21"/>
-    <row r="675" ht="15.75" customHeight="1" s="21"/>
-    <row r="676" ht="15.75" customHeight="1" s="21"/>
-    <row r="677" ht="15.75" customHeight="1" s="21"/>
-    <row r="678" ht="15.75" customHeight="1" s="21"/>
-    <row r="679" ht="15.75" customHeight="1" s="21"/>
-    <row r="680" ht="15.75" customHeight="1" s="21"/>
-    <row r="681" ht="15.75" customHeight="1" s="21"/>
-    <row r="682" ht="15.75" customHeight="1" s="21"/>
-    <row r="683" ht="15.75" customHeight="1" s="21"/>
-    <row r="684" ht="15.75" customHeight="1" s="21"/>
-    <row r="685" ht="15.75" customHeight="1" s="21"/>
-    <row r="686" ht="15.75" customHeight="1" s="21"/>
-    <row r="687" ht="15.75" customHeight="1" s="21"/>
-    <row r="688" ht="15.75" customHeight="1" s="21"/>
-    <row r="689" ht="15.75" customHeight="1" s="21"/>
-    <row r="690" ht="15.75" customHeight="1" s="21"/>
-    <row r="691" ht="15.75" customHeight="1" s="21"/>
-    <row r="692" ht="15.75" customHeight="1" s="21"/>
-    <row r="693" ht="15.75" customHeight="1" s="21"/>
-    <row r="694" ht="15.75" customHeight="1" s="21"/>
-    <row r="695" ht="15.75" customHeight="1" s="21"/>
-    <row r="696" ht="15.75" customHeight="1" s="21"/>
-    <row r="697" ht="15.75" customHeight="1" s="21"/>
-    <row r="698" ht="15.75" customHeight="1" s="21"/>
-    <row r="699" ht="15.75" customHeight="1" s="21"/>
-    <row r="700" ht="15.75" customHeight="1" s="21"/>
-    <row r="701" ht="15.75" customHeight="1" s="21"/>
-    <row r="702" ht="15.75" customHeight="1" s="21"/>
-    <row r="703" ht="15.75" customHeight="1" s="21"/>
-    <row r="704" ht="15.75" customHeight="1" s="21"/>
-    <row r="705" ht="15.75" customHeight="1" s="21"/>
-    <row r="706" ht="15.75" customHeight="1" s="21"/>
-    <row r="707" ht="15.75" customHeight="1" s="21"/>
-    <row r="708" ht="15.75" customHeight="1" s="21"/>
-    <row r="709" ht="15.75" customHeight="1" s="21"/>
-    <row r="710" ht="15.75" customHeight="1" s="21"/>
-    <row r="711" ht="15.75" customHeight="1" s="21"/>
-    <row r="712" ht="15.75" customHeight="1" s="21"/>
-    <row r="713" ht="15.75" customHeight="1" s="21"/>
-    <row r="714" ht="15.75" customHeight="1" s="21"/>
-    <row r="715" ht="15.75" customHeight="1" s="21"/>
-    <row r="716" ht="15.75" customHeight="1" s="21"/>
-    <row r="717" ht="15.75" customHeight="1" s="21"/>
-    <row r="718" ht="15.75" customHeight="1" s="21"/>
-    <row r="719" ht="15.75" customHeight="1" s="21"/>
-    <row r="720" ht="15.75" customHeight="1" s="21"/>
-    <row r="721" ht="15.75" customHeight="1" s="21"/>
-    <row r="722" ht="15.75" customHeight="1" s="21"/>
-    <row r="723" ht="15.75" customHeight="1" s="21"/>
-    <row r="724" ht="15.75" customHeight="1" s="21"/>
-    <row r="725" ht="15.75" customHeight="1" s="21"/>
-    <row r="726" ht="15.75" customHeight="1" s="21"/>
-    <row r="727" ht="15.75" customHeight="1" s="21"/>
-    <row r="728" ht="15.75" customHeight="1" s="21"/>
-    <row r="729" ht="15.75" customHeight="1" s="21"/>
-    <row r="730" ht="15.75" customHeight="1" s="21"/>
-    <row r="731" ht="15.75" customHeight="1" s="21"/>
-    <row r="732" ht="15.75" customHeight="1" s="21"/>
-    <row r="733" ht="15.75" customHeight="1" s="21"/>
-    <row r="734" ht="15.75" customHeight="1" s="21"/>
-    <row r="735" ht="15.75" customHeight="1" s="21"/>
-    <row r="736" ht="15.75" customHeight="1" s="21"/>
-    <row r="737" ht="15.75" customHeight="1" s="21"/>
-    <row r="738" ht="15.75" customHeight="1" s="21"/>
-    <row r="739" ht="15.75" customHeight="1" s="21"/>
-    <row r="740" ht="15.75" customHeight="1" s="21"/>
-    <row r="741" ht="15.75" customHeight="1" s="21"/>
-    <row r="742" ht="15.75" customHeight="1" s="21"/>
-    <row r="743" ht="15.75" customHeight="1" s="21"/>
-    <row r="744" ht="15.75" customHeight="1" s="21"/>
-    <row r="745" ht="15.75" customHeight="1" s="21"/>
-    <row r="746" ht="15.75" customHeight="1" s="21"/>
-    <row r="747" ht="15.75" customHeight="1" s="21"/>
-    <row r="748" ht="15.75" customHeight="1" s="21"/>
-    <row r="749" ht="15.75" customHeight="1" s="21"/>
-    <row r="750" ht="15.75" customHeight="1" s="21"/>
-    <row r="751" ht="15.75" customHeight="1" s="21"/>
-    <row r="752" ht="15.75" customHeight="1" s="21"/>
-    <row r="753" ht="15.75" customHeight="1" s="21"/>
-    <row r="754" ht="15.75" customHeight="1" s="21"/>
-    <row r="755" ht="15.75" customHeight="1" s="21"/>
-    <row r="756" ht="15.75" customHeight="1" s="21"/>
-    <row r="757" ht="15.75" customHeight="1" s="21"/>
-    <row r="758" ht="15.75" customHeight="1" s="21"/>
-    <row r="759" ht="15.75" customHeight="1" s="21"/>
-    <row r="760" ht="15.75" customHeight="1" s="21"/>
-    <row r="761" ht="15.75" customHeight="1" s="21"/>
-    <row r="762" ht="15.75" customHeight="1" s="21"/>
-    <row r="763" ht="15.75" customHeight="1" s="21"/>
-    <row r="764" ht="15.75" customHeight="1" s="21"/>
-    <row r="765" ht="15.75" customHeight="1" s="21"/>
-    <row r="766" ht="15.75" customHeight="1" s="21"/>
-    <row r="767" ht="15.75" customHeight="1" s="21"/>
-    <row r="768" ht="15.75" customHeight="1" s="21"/>
-    <row r="769" ht="15.75" customHeight="1" s="21"/>
-    <row r="770" ht="15.75" customHeight="1" s="21"/>
-    <row r="771" ht="15.75" customHeight="1" s="21"/>
-    <row r="772" ht="15.75" customHeight="1" s="21"/>
-    <row r="773" ht="15.75" customHeight="1" s="21"/>
-    <row r="774" ht="15.75" customHeight="1" s="21"/>
-    <row r="775" ht="15.75" customHeight="1" s="21"/>
-    <row r="776" ht="15.75" customHeight="1" s="21"/>
-    <row r="777" ht="15.75" customHeight="1" s="21"/>
-    <row r="778" ht="15.75" customHeight="1" s="21"/>
-    <row r="779" ht="15.75" customHeight="1" s="21"/>
-    <row r="780" ht="15.75" customHeight="1" s="21"/>
-    <row r="781" ht="15.75" customHeight="1" s="21"/>
-    <row r="782" ht="15.75" customHeight="1" s="21"/>
-    <row r="783" ht="15.75" customHeight="1" s="21"/>
-    <row r="784" ht="15.75" customHeight="1" s="21"/>
-    <row r="785" ht="15.75" customHeight="1" s="21"/>
-    <row r="786" ht="15.75" customHeight="1" s="21"/>
-    <row r="787" ht="15.75" customHeight="1" s="21"/>
-    <row r="788" ht="15.75" customHeight="1" s="21"/>
-    <row r="789" ht="15.75" customHeight="1" s="21"/>
-    <row r="790" ht="15.75" customHeight="1" s="21"/>
-    <row r="791" ht="15.75" customHeight="1" s="21"/>
-    <row r="792" ht="15.75" customHeight="1" s="21"/>
-    <row r="793" ht="15.75" customHeight="1" s="21"/>
-    <row r="794" ht="15.75" customHeight="1" s="21"/>
-    <row r="795" ht="15.75" customHeight="1" s="21"/>
-    <row r="796" ht="15.75" customHeight="1" s="21"/>
-    <row r="797" ht="15.75" customHeight="1" s="21"/>
-    <row r="798" ht="15.75" customHeight="1" s="21"/>
-    <row r="799" ht="15.75" customHeight="1" s="21"/>
-    <row r="800" ht="15.75" customHeight="1" s="21"/>
-    <row r="801" ht="15.75" customHeight="1" s="21"/>
-    <row r="802" ht="15.75" customHeight="1" s="21"/>
-    <row r="803" ht="15.75" customHeight="1" s="21"/>
-    <row r="804" ht="15.75" customHeight="1" s="21"/>
-    <row r="805" ht="15.75" customHeight="1" s="21"/>
-    <row r="806" ht="15.75" customHeight="1" s="21"/>
-    <row r="807" ht="15.75" customHeight="1" s="21"/>
-    <row r="808" ht="15.75" customHeight="1" s="21"/>
-    <row r="809" ht="15.75" customHeight="1" s="21"/>
-    <row r="810" ht="15.75" customHeight="1" s="21"/>
-    <row r="811" ht="15.75" customHeight="1" s="21"/>
-    <row r="812" ht="15.75" customHeight="1" s="21"/>
-    <row r="813" ht="15.75" customHeight="1" s="21"/>
-    <row r="814" ht="15.75" customHeight="1" s="21"/>
-    <row r="815" ht="15.75" customHeight="1" s="21"/>
-    <row r="816" ht="15.75" customHeight="1" s="21"/>
-    <row r="817" ht="15.75" customHeight="1" s="21"/>
-    <row r="818" ht="15.75" customHeight="1" s="21"/>
-    <row r="819" ht="15.75" customHeight="1" s="21"/>
-    <row r="820" ht="15.75" customHeight="1" s="21"/>
-    <row r="821" ht="15.75" customHeight="1" s="21"/>
-    <row r="822" ht="15.75" customHeight="1" s="21"/>
-    <row r="823" ht="15.75" customHeight="1" s="21"/>
-    <row r="824" ht="15.75" customHeight="1" s="21"/>
-    <row r="825" ht="15.75" customHeight="1" s="21"/>
-    <row r="826" ht="15.75" customHeight="1" s="21"/>
-    <row r="827" ht="15.75" customHeight="1" s="21"/>
-    <row r="828" ht="15.75" customHeight="1" s="21"/>
-    <row r="829" ht="15.75" customHeight="1" s="21"/>
-    <row r="830" ht="15.75" customHeight="1" s="21"/>
-    <row r="831" ht="15.75" customHeight="1" s="21"/>
-    <row r="832" ht="15.75" customHeight="1" s="21"/>
-    <row r="833" ht="15.75" customHeight="1" s="21"/>
-    <row r="834" ht="15.75" customHeight="1" s="21"/>
-    <row r="835" ht="15.75" customHeight="1" s="21"/>
-    <row r="836" ht="15.75" customHeight="1" s="21"/>
-    <row r="837" ht="15.75" customHeight="1" s="21"/>
-    <row r="838" ht="15.75" customHeight="1" s="21"/>
-    <row r="839" ht="15.75" customHeight="1" s="21"/>
-    <row r="840" ht="15.75" customHeight="1" s="21"/>
-    <row r="841" ht="15.75" customHeight="1" s="21"/>
-    <row r="842" ht="15.75" customHeight="1" s="21"/>
-    <row r="843" ht="15.75" customHeight="1" s="21"/>
-    <row r="844" ht="15.75" customHeight="1" s="21"/>
-    <row r="845" ht="15.75" customHeight="1" s="21"/>
-    <row r="846" ht="15.75" customHeight="1" s="21"/>
-    <row r="847" ht="15.75" customHeight="1" s="21"/>
-    <row r="848" ht="15.75" customHeight="1" s="21"/>
-    <row r="849" ht="15.75" customHeight="1" s="21"/>
-    <row r="850" ht="15.75" customHeight="1" s="21"/>
-    <row r="851" ht="15.75" customHeight="1" s="21"/>
-    <row r="852" ht="15.75" customHeight="1" s="21"/>
-    <row r="853" ht="15.75" customHeight="1" s="21"/>
-    <row r="854" ht="15.75" customHeight="1" s="21"/>
-    <row r="855" ht="15.75" customHeight="1" s="21"/>
-    <row r="856" ht="15.75" customHeight="1" s="21"/>
-    <row r="857" ht="15.75" customHeight="1" s="21"/>
-    <row r="858" ht="15.75" customHeight="1" s="21"/>
-    <row r="859" ht="15.75" customHeight="1" s="21"/>
-    <row r="860" ht="15.75" customHeight="1" s="21"/>
-    <row r="861" ht="15.75" customHeight="1" s="21"/>
-    <row r="862" ht="15.75" customHeight="1" s="21"/>
-    <row r="863" ht="15.75" customHeight="1" s="21"/>
-    <row r="864" ht="15.75" customHeight="1" s="21"/>
-    <row r="865" ht="15.75" customHeight="1" s="21"/>
-    <row r="866" ht="15.75" customHeight="1" s="21"/>
-    <row r="867" ht="15.75" customHeight="1" s="21"/>
-    <row r="868" ht="15.75" customHeight="1" s="21"/>
-    <row r="869" ht="15.75" customHeight="1" s="21"/>
-    <row r="870" ht="15.75" customHeight="1" s="21"/>
-    <row r="871" ht="15.75" customHeight="1" s="21"/>
-    <row r="872" ht="15.75" customHeight="1" s="21"/>
-    <row r="873" ht="15.75" customHeight="1" s="21"/>
-    <row r="874" ht="15.75" customHeight="1" s="21"/>
-    <row r="875" ht="15.75" customHeight="1" s="21"/>
-    <row r="876" ht="15.75" customHeight="1" s="21"/>
-    <row r="877" ht="15.75" customHeight="1" s="21"/>
-    <row r="878" ht="15.75" customHeight="1" s="21"/>
-    <row r="879" ht="15.75" customHeight="1" s="21"/>
-    <row r="880" ht="15.75" customHeight="1" s="21"/>
-    <row r="881" ht="15.75" customHeight="1" s="21"/>
-    <row r="882" ht="15.75" customHeight="1" s="21"/>
-    <row r="883" ht="15.75" customHeight="1" s="21"/>
-    <row r="884" ht="15.75" customHeight="1" s="21"/>
-    <row r="885" ht="15.75" customHeight="1" s="21"/>
-    <row r="886" ht="15.75" customHeight="1" s="21"/>
-    <row r="887" ht="15.75" customHeight="1" s="21"/>
-    <row r="888" ht="15.75" customHeight="1" s="21"/>
-    <row r="889" ht="15.75" customHeight="1" s="21"/>
-    <row r="890" ht="15.75" customHeight="1" s="21"/>
-    <row r="891" ht="15.75" customHeight="1" s="21"/>
-    <row r="892" ht="15.75" customHeight="1" s="21"/>
-    <row r="893" ht="15.75" customHeight="1" s="21"/>
-    <row r="894" ht="15.75" customHeight="1" s="21"/>
-    <row r="895" ht="15.75" customHeight="1" s="21"/>
-    <row r="896" ht="15.75" customHeight="1" s="21"/>
-    <row r="897" ht="15.75" customHeight="1" s="21"/>
-    <row r="898" ht="15.75" customHeight="1" s="21"/>
-    <row r="899" ht="15.75" customHeight="1" s="21"/>
-    <row r="900" ht="15.75" customHeight="1" s="21"/>
-    <row r="901" ht="15.75" customHeight="1" s="21"/>
-    <row r="902" ht="15.75" customHeight="1" s="21"/>
-    <row r="903" ht="15.75" customHeight="1" s="21"/>
-    <row r="904" ht="15.75" customHeight="1" s="21"/>
-    <row r="905" ht="15.75" customHeight="1" s="21"/>
-    <row r="906" ht="15.75" customHeight="1" s="21"/>
-    <row r="907" ht="15.75" customHeight="1" s="21"/>
-    <row r="908" ht="15.75" customHeight="1" s="21"/>
-    <row r="909" ht="15.75" customHeight="1" s="21"/>
-    <row r="910" ht="15.75" customHeight="1" s="21"/>
-    <row r="911" ht="15.75" customHeight="1" s="21"/>
-    <row r="912" ht="15.75" customHeight="1" s="21"/>
-    <row r="913" ht="15.75" customHeight="1" s="21"/>
-    <row r="914" ht="15.75" customHeight="1" s="21"/>
-    <row r="915" ht="15.75" customHeight="1" s="21"/>
-    <row r="916" ht="15.75" customHeight="1" s="21"/>
-    <row r="917" ht="15.75" customHeight="1" s="21"/>
-    <row r="918" ht="15.75" customHeight="1" s="21"/>
-    <row r="919" ht="15.75" customHeight="1" s="21"/>
-    <row r="920" ht="15.75" customHeight="1" s="21"/>
-    <row r="921" ht="15.75" customHeight="1" s="21"/>
-    <row r="922" ht="15.75" customHeight="1" s="21"/>
-    <row r="923" ht="15.75" customHeight="1" s="21"/>
-    <row r="924" ht="15.75" customHeight="1" s="21"/>
-    <row r="925" ht="15.75" customHeight="1" s="21"/>
-    <row r="926" ht="15.75" customHeight="1" s="21"/>
-    <row r="927" ht="15.75" customHeight="1" s="21"/>
-    <row r="928" ht="15.75" customHeight="1" s="21"/>
-    <row r="929" ht="15.75" customHeight="1" s="21"/>
-    <row r="930" ht="15.75" customHeight="1" s="21"/>
-    <row r="931" ht="15.75" customHeight="1" s="21"/>
-    <row r="932" ht="15.75" customHeight="1" s="21"/>
-    <row r="933" ht="15.75" customHeight="1" s="21"/>
-    <row r="934" ht="15.75" customHeight="1" s="21"/>
-    <row r="935" ht="15.75" customHeight="1" s="21"/>
-    <row r="936" ht="15.75" customHeight="1" s="21"/>
-    <row r="937" ht="15.75" customHeight="1" s="21"/>
-    <row r="938" ht="15.75" customHeight="1" s="21"/>
-    <row r="939" ht="15.75" customHeight="1" s="21"/>
-    <row r="940" ht="15.75" customHeight="1" s="21"/>
-    <row r="941" ht="15.75" customHeight="1" s="21"/>
-    <row r="942" ht="15.75" customHeight="1" s="21"/>
-    <row r="943" ht="15.75" customHeight="1" s="21"/>
-    <row r="944" ht="15.75" customHeight="1" s="21"/>
-    <row r="945" ht="15.75" customHeight="1" s="21"/>
-    <row r="946" ht="15.75" customHeight="1" s="21"/>
-    <row r="947" ht="15.75" customHeight="1" s="21"/>
-    <row r="948" ht="15.75" customHeight="1" s="21"/>
-    <row r="949" ht="15.75" customHeight="1" s="21"/>
-    <row r="950" ht="15.75" customHeight="1" s="21"/>
-    <row r="951" ht="15.75" customHeight="1" s="21"/>
-    <row r="952" ht="15.75" customHeight="1" s="21"/>
-    <row r="953" ht="15.75" customHeight="1" s="21"/>
-    <row r="954" ht="15.75" customHeight="1" s="21"/>
-    <row r="955" ht="15.75" customHeight="1" s="21"/>
-    <row r="956" ht="15.75" customHeight="1" s="21"/>
-    <row r="957" ht="15.75" customHeight="1" s="21"/>
-    <row r="958" ht="15.75" customHeight="1" s="21"/>
-    <row r="959" ht="15.75" customHeight="1" s="21"/>
-    <row r="960" ht="15.75" customHeight="1" s="21"/>
-    <row r="961" ht="15.75" customHeight="1" s="21"/>
-    <row r="962" ht="15.75" customHeight="1" s="21"/>
-    <row r="963" ht="15.75" customHeight="1" s="21"/>
-    <row r="964" ht="15.75" customHeight="1" s="21"/>
-    <row r="965" ht="15.75" customHeight="1" s="21"/>
-    <row r="966" ht="15.75" customHeight="1" s="21"/>
-    <row r="967" ht="15.75" customHeight="1" s="21"/>
-    <row r="968" ht="15.75" customHeight="1" s="21"/>
-    <row r="969" ht="15.75" customHeight="1" s="21"/>
-    <row r="970" ht="15.75" customHeight="1" s="21"/>
-    <row r="971" ht="15.75" customHeight="1" s="21"/>
-    <row r="972" ht="15.75" customHeight="1" s="21"/>
-    <row r="973" ht="15.75" customHeight="1" s="21"/>
-    <row r="974" ht="15.75" customHeight="1" s="21"/>
-    <row r="975" ht="15.75" customHeight="1" s="21"/>
-    <row r="976" ht="15.75" customHeight="1" s="21"/>
-    <row r="977" ht="15.75" customHeight="1" s="21"/>
-    <row r="978" ht="15.75" customHeight="1" s="21"/>
-    <row r="979" ht="15.75" customHeight="1" s="21"/>
-    <row r="980" ht="15.75" customHeight="1" s="21"/>
-    <row r="981" ht="15.75" customHeight="1" s="21"/>
-    <row r="982" ht="15.75" customHeight="1" s="21"/>
-    <row r="983" ht="15.75" customHeight="1" s="21"/>
-    <row r="984" ht="15.75" customHeight="1" s="21"/>
-    <row r="985" ht="15.75" customHeight="1" s="21"/>
-    <row r="986" ht="15.75" customHeight="1" s="21"/>
-    <row r="987" ht="15.75" customHeight="1" s="21"/>
-    <row r="988" ht="15.75" customHeight="1" s="21"/>
-    <row r="989" ht="15.75" customHeight="1" s="21"/>
-    <row r="990" ht="15.75" customHeight="1" s="21"/>
-    <row r="991" ht="15.75" customHeight="1" s="21"/>
-    <row r="992" ht="15.75" customHeight="1" s="21"/>
-    <row r="993" ht="15.75" customHeight="1" s="21"/>
-    <row r="994" ht="15.75" customHeight="1" s="21"/>
-    <row r="995" ht="15.75" customHeight="1" s="21"/>
-    <row r="996" ht="15.75" customHeight="1" s="21"/>
-    <row r="997" ht="15.75" customHeight="1" s="21"/>
-    <row r="998" ht="15.75" customHeight="1" s="21"/>
-    <row r="999" ht="15.75" customHeight="1" s="21"/>
-    <row r="1000" ht="15.75" customHeight="1" s="21"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -21541,16 +21556,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="20" customWidth="1" style="21" min="1" max="1"/>
-    <col width="55" customWidth="1" style="21" min="2" max="2"/>
-    <col width="20" customWidth="1" style="21" min="3" max="3"/>
-    <col width="55" customWidth="1" style="21" min="4" max="4"/>
-    <col width="8.710000000000001" customWidth="1" style="21" min="5" max="26"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="8.7109375" customWidth="1" min="5" max="26"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Protocol-Level Tier</t>
@@ -21572,7 +21587,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="75" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Basic</t>
@@ -21594,7 +21609,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="75" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Advanced</t>
@@ -21616,7 +21631,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -21638,7 +21653,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Advanced</t>
@@ -21650,7 +21665,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Mode Column</t>
@@ -21694,7 +21709,7 @@
       </c>
       <c r="B12" s="1" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21718,986 +21733,986 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="21"/>
-    <row r="22" ht="15.75" customHeight="1" s="21"/>
-    <row r="23" ht="15.75" customHeight="1" s="21"/>
-    <row r="24" ht="15.75" customHeight="1" s="21"/>
-    <row r="25" ht="15.75" customHeight="1" s="21"/>
-    <row r="26" ht="15.75" customHeight="1" s="21"/>
-    <row r="27" ht="15.75" customHeight="1" s="21"/>
-    <row r="28" ht="15.75" customHeight="1" s="21"/>
-    <row r="29" ht="15.75" customHeight="1" s="21"/>
-    <row r="30" ht="15.75" customHeight="1" s="21"/>
-    <row r="31" ht="15.75" customHeight="1" s="21"/>
-    <row r="32" ht="15.75" customHeight="1" s="21"/>
-    <row r="33" ht="15.75" customHeight="1" s="21"/>
-    <row r="34" ht="15.75" customHeight="1" s="21"/>
-    <row r="35" ht="15.75" customHeight="1" s="21"/>
-    <row r="36" ht="15.75" customHeight="1" s="21"/>
-    <row r="37" ht="15.75" customHeight="1" s="21"/>
-    <row r="38" ht="15.75" customHeight="1" s="21"/>
-    <row r="39" ht="15.75" customHeight="1" s="21"/>
-    <row r="40" ht="15.75" customHeight="1" s="21"/>
-    <row r="41" ht="15.75" customHeight="1" s="21"/>
-    <row r="42" ht="15.75" customHeight="1" s="21"/>
-    <row r="43" ht="15.75" customHeight="1" s="21"/>
-    <row r="44" ht="15.75" customHeight="1" s="21"/>
-    <row r="45" ht="15.75" customHeight="1" s="21"/>
-    <row r="46" ht="15.75" customHeight="1" s="21"/>
-    <row r="47" ht="15.75" customHeight="1" s="21"/>
-    <row r="48" ht="15.75" customHeight="1" s="21"/>
-    <row r="49" ht="15.75" customHeight="1" s="21"/>
-    <row r="50" ht="15.75" customHeight="1" s="21"/>
-    <row r="51" ht="15.75" customHeight="1" s="21"/>
-    <row r="52" ht="15.75" customHeight="1" s="21"/>
-    <row r="53" ht="15.75" customHeight="1" s="21"/>
-    <row r="54" ht="15.75" customHeight="1" s="21"/>
-    <row r="55" ht="15.75" customHeight="1" s="21"/>
-    <row r="56" ht="15.75" customHeight="1" s="21"/>
-    <row r="57" ht="15.75" customHeight="1" s="21"/>
-    <row r="58" ht="15.75" customHeight="1" s="21"/>
-    <row r="59" ht="15.75" customHeight="1" s="21"/>
-    <row r="60" ht="15.75" customHeight="1" s="21"/>
-    <row r="61" ht="15.75" customHeight="1" s="21"/>
-    <row r="62" ht="15.75" customHeight="1" s="21"/>
-    <row r="63" ht="15.75" customHeight="1" s="21"/>
-    <row r="64" ht="15.75" customHeight="1" s="21"/>
-    <row r="65" ht="15.75" customHeight="1" s="21"/>
-    <row r="66" ht="15.75" customHeight="1" s="21"/>
-    <row r="67" ht="15.75" customHeight="1" s="21"/>
-    <row r="68" ht="15.75" customHeight="1" s="21"/>
-    <row r="69" ht="15.75" customHeight="1" s="21"/>
-    <row r="70" ht="15.75" customHeight="1" s="21"/>
-    <row r="71" ht="15.75" customHeight="1" s="21"/>
-    <row r="72" ht="15.75" customHeight="1" s="21"/>
-    <row r="73" ht="15.75" customHeight="1" s="21"/>
-    <row r="74" ht="15.75" customHeight="1" s="21"/>
-    <row r="75" ht="15.75" customHeight="1" s="21"/>
-    <row r="76" ht="15.75" customHeight="1" s="21"/>
-    <row r="77" ht="15.75" customHeight="1" s="21"/>
-    <row r="78" ht="15.75" customHeight="1" s="21"/>
-    <row r="79" ht="15.75" customHeight="1" s="21"/>
-    <row r="80" ht="15.75" customHeight="1" s="21"/>
-    <row r="81" ht="15.75" customHeight="1" s="21"/>
-    <row r="82" ht="15.75" customHeight="1" s="21"/>
-    <row r="83" ht="15.75" customHeight="1" s="21"/>
-    <row r="84" ht="15.75" customHeight="1" s="21"/>
-    <row r="85" ht="15.75" customHeight="1" s="21"/>
-    <row r="86" ht="15.75" customHeight="1" s="21"/>
-    <row r="87" ht="15.75" customHeight="1" s="21"/>
-    <row r="88" ht="15.75" customHeight="1" s="21"/>
-    <row r="89" ht="15.75" customHeight="1" s="21"/>
-    <row r="90" ht="15.75" customHeight="1" s="21"/>
-    <row r="91" ht="15.75" customHeight="1" s="21"/>
-    <row r="92" ht="15.75" customHeight="1" s="21"/>
-    <row r="93" ht="15.75" customHeight="1" s="21"/>
-    <row r="94" ht="15.75" customHeight="1" s="21"/>
-    <row r="95" ht="15.75" customHeight="1" s="21"/>
-    <row r="96" ht="15.75" customHeight="1" s="21"/>
-    <row r="97" ht="15.75" customHeight="1" s="21"/>
-    <row r="98" ht="15.75" customHeight="1" s="21"/>
-    <row r="99" ht="15.75" customHeight="1" s="21"/>
-    <row r="100" ht="15.75" customHeight="1" s="21"/>
-    <row r="101" ht="15.75" customHeight="1" s="21"/>
-    <row r="102" ht="15.75" customHeight="1" s="21"/>
-    <row r="103" ht="15.75" customHeight="1" s="21"/>
-    <row r="104" ht="15.75" customHeight="1" s="21"/>
-    <row r="105" ht="15.75" customHeight="1" s="21"/>
-    <row r="106" ht="15.75" customHeight="1" s="21"/>
-    <row r="107" ht="15.75" customHeight="1" s="21"/>
-    <row r="108" ht="15.75" customHeight="1" s="21"/>
-    <row r="109" ht="15.75" customHeight="1" s="21"/>
-    <row r="110" ht="15.75" customHeight="1" s="21"/>
-    <row r="111" ht="15.75" customHeight="1" s="21"/>
-    <row r="112" ht="15.75" customHeight="1" s="21"/>
-    <row r="113" ht="15.75" customHeight="1" s="21"/>
-    <row r="114" ht="15.75" customHeight="1" s="21"/>
-    <row r="115" ht="15.75" customHeight="1" s="21"/>
-    <row r="116" ht="15.75" customHeight="1" s="21"/>
-    <row r="117" ht="15.75" customHeight="1" s="21"/>
-    <row r="118" ht="15.75" customHeight="1" s="21"/>
-    <row r="119" ht="15.75" customHeight="1" s="21"/>
-    <row r="120" ht="15.75" customHeight="1" s="21"/>
-    <row r="121" ht="15.75" customHeight="1" s="21"/>
-    <row r="122" ht="15.75" customHeight="1" s="21"/>
-    <row r="123" ht="15.75" customHeight="1" s="21"/>
-    <row r="124" ht="15.75" customHeight="1" s="21"/>
-    <row r="125" ht="15.75" customHeight="1" s="21"/>
-    <row r="126" ht="15.75" customHeight="1" s="21"/>
-    <row r="127" ht="15.75" customHeight="1" s="21"/>
-    <row r="128" ht="15.75" customHeight="1" s="21"/>
-    <row r="129" ht="15.75" customHeight="1" s="21"/>
-    <row r="130" ht="15.75" customHeight="1" s="21"/>
-    <row r="131" ht="15.75" customHeight="1" s="21"/>
-    <row r="132" ht="15.75" customHeight="1" s="21"/>
-    <row r="133" ht="15.75" customHeight="1" s="21"/>
-    <row r="134" ht="15.75" customHeight="1" s="21"/>
-    <row r="135" ht="15.75" customHeight="1" s="21"/>
-    <row r="136" ht="15.75" customHeight="1" s="21"/>
-    <row r="137" ht="15.75" customHeight="1" s="21"/>
-    <row r="138" ht="15.75" customHeight="1" s="21"/>
-    <row r="139" ht="15.75" customHeight="1" s="21"/>
-    <row r="140" ht="15.75" customHeight="1" s="21"/>
-    <row r="141" ht="15.75" customHeight="1" s="21"/>
-    <row r="142" ht="15.75" customHeight="1" s="21"/>
-    <row r="143" ht="15.75" customHeight="1" s="21"/>
-    <row r="144" ht="15.75" customHeight="1" s="21"/>
-    <row r="145" ht="15.75" customHeight="1" s="21"/>
-    <row r="146" ht="15.75" customHeight="1" s="21"/>
-    <row r="147" ht="15.75" customHeight="1" s="21"/>
-    <row r="148" ht="15.75" customHeight="1" s="21"/>
-    <row r="149" ht="15.75" customHeight="1" s="21"/>
-    <row r="150" ht="15.75" customHeight="1" s="21"/>
-    <row r="151" ht="15.75" customHeight="1" s="21"/>
-    <row r="152" ht="15.75" customHeight="1" s="21"/>
-    <row r="153" ht="15.75" customHeight="1" s="21"/>
-    <row r="154" ht="15.75" customHeight="1" s="21"/>
-    <row r="155" ht="15.75" customHeight="1" s="21"/>
-    <row r="156" ht="15.75" customHeight="1" s="21"/>
-    <row r="157" ht="15.75" customHeight="1" s="21"/>
-    <row r="158" ht="15.75" customHeight="1" s="21"/>
-    <row r="159" ht="15.75" customHeight="1" s="21"/>
-    <row r="160" ht="15.75" customHeight="1" s="21"/>
-    <row r="161" ht="15.75" customHeight="1" s="21"/>
-    <row r="162" ht="15.75" customHeight="1" s="21"/>
-    <row r="163" ht="15.75" customHeight="1" s="21"/>
-    <row r="164" ht="15.75" customHeight="1" s="21"/>
-    <row r="165" ht="15.75" customHeight="1" s="21"/>
-    <row r="166" ht="15.75" customHeight="1" s="21"/>
-    <row r="167" ht="15.75" customHeight="1" s="21"/>
-    <row r="168" ht="15.75" customHeight="1" s="21"/>
-    <row r="169" ht="15.75" customHeight="1" s="21"/>
-    <row r="170" ht="15.75" customHeight="1" s="21"/>
-    <row r="171" ht="15.75" customHeight="1" s="21"/>
-    <row r="172" ht="15.75" customHeight="1" s="21"/>
-    <row r="173" ht="15.75" customHeight="1" s="21"/>
-    <row r="174" ht="15.75" customHeight="1" s="21"/>
-    <row r="175" ht="15.75" customHeight="1" s="21"/>
-    <row r="176" ht="15.75" customHeight="1" s="21"/>
-    <row r="177" ht="15.75" customHeight="1" s="21"/>
-    <row r="178" ht="15.75" customHeight="1" s="21"/>
-    <row r="179" ht="15.75" customHeight="1" s="21"/>
-    <row r="180" ht="15.75" customHeight="1" s="21"/>
-    <row r="181" ht="15.75" customHeight="1" s="21"/>
-    <row r="182" ht="15.75" customHeight="1" s="21"/>
-    <row r="183" ht="15.75" customHeight="1" s="21"/>
-    <row r="184" ht="15.75" customHeight="1" s="21"/>
-    <row r="185" ht="15.75" customHeight="1" s="21"/>
-    <row r="186" ht="15.75" customHeight="1" s="21"/>
-    <row r="187" ht="15.75" customHeight="1" s="21"/>
-    <row r="188" ht="15.75" customHeight="1" s="21"/>
-    <row r="189" ht="15.75" customHeight="1" s="21"/>
-    <row r="190" ht="15.75" customHeight="1" s="21"/>
-    <row r="191" ht="15.75" customHeight="1" s="21"/>
-    <row r="192" ht="15.75" customHeight="1" s="21"/>
-    <row r="193" ht="15.75" customHeight="1" s="21"/>
-    <row r="194" ht="15.75" customHeight="1" s="21"/>
-    <row r="195" ht="15.75" customHeight="1" s="21"/>
-    <row r="196" ht="15.75" customHeight="1" s="21"/>
-    <row r="197" ht="15.75" customHeight="1" s="21"/>
-    <row r="198" ht="15.75" customHeight="1" s="21"/>
-    <row r="199" ht="15.75" customHeight="1" s="21"/>
-    <row r="200" ht="15.75" customHeight="1" s="21"/>
-    <row r="201" ht="15.75" customHeight="1" s="21"/>
-    <row r="202" ht="15.75" customHeight="1" s="21"/>
-    <row r="203" ht="15.75" customHeight="1" s="21"/>
-    <row r="204" ht="15.75" customHeight="1" s="21"/>
-    <row r="205" ht="15.75" customHeight="1" s="21"/>
-    <row r="206" ht="15.75" customHeight="1" s="21"/>
-    <row r="207" ht="15.75" customHeight="1" s="21"/>
-    <row r="208" ht="15.75" customHeight="1" s="21"/>
-    <row r="209" ht="15.75" customHeight="1" s="21"/>
-    <row r="210" ht="15.75" customHeight="1" s="21"/>
-    <row r="211" ht="15.75" customHeight="1" s="21"/>
-    <row r="212" ht="15.75" customHeight="1" s="21"/>
-    <row r="213" ht="15.75" customHeight="1" s="21"/>
-    <row r="214" ht="15.75" customHeight="1" s="21"/>
-    <row r="215" ht="15.75" customHeight="1" s="21"/>
-    <row r="216" ht="15.75" customHeight="1" s="21"/>
-    <row r="217" ht="15.75" customHeight="1" s="21"/>
-    <row r="218" ht="15.75" customHeight="1" s="21"/>
-    <row r="219" ht="15.75" customHeight="1" s="21"/>
-    <row r="220" ht="15.75" customHeight="1" s="21"/>
-    <row r="221" ht="15.75" customHeight="1" s="21"/>
-    <row r="222" ht="15.75" customHeight="1" s="21"/>
-    <row r="223" ht="15.75" customHeight="1" s="21"/>
-    <row r="224" ht="15.75" customHeight="1" s="21"/>
-    <row r="225" ht="15.75" customHeight="1" s="21"/>
-    <row r="226" ht="15.75" customHeight="1" s="21"/>
-    <row r="227" ht="15.75" customHeight="1" s="21"/>
-    <row r="228" ht="15.75" customHeight="1" s="21"/>
-    <row r="229" ht="15.75" customHeight="1" s="21"/>
-    <row r="230" ht="15.75" customHeight="1" s="21"/>
-    <row r="231" ht="15.75" customHeight="1" s="21"/>
-    <row r="232" ht="15.75" customHeight="1" s="21"/>
-    <row r="233" ht="15.75" customHeight="1" s="21"/>
-    <row r="234" ht="15.75" customHeight="1" s="21"/>
-    <row r="235" ht="15.75" customHeight="1" s="21"/>
-    <row r="236" ht="15.75" customHeight="1" s="21"/>
-    <row r="237" ht="15.75" customHeight="1" s="21"/>
-    <row r="238" ht="15.75" customHeight="1" s="21"/>
-    <row r="239" ht="15.75" customHeight="1" s="21"/>
-    <row r="240" ht="15.75" customHeight="1" s="21"/>
-    <row r="241" ht="15.75" customHeight="1" s="21"/>
-    <row r="242" ht="15.75" customHeight="1" s="21"/>
-    <row r="243" ht="15.75" customHeight="1" s="21"/>
-    <row r="244" ht="15.75" customHeight="1" s="21"/>
-    <row r="245" ht="15.75" customHeight="1" s="21"/>
-    <row r="246" ht="15.75" customHeight="1" s="21"/>
-    <row r="247" ht="15.75" customHeight="1" s="21"/>
-    <row r="248" ht="15.75" customHeight="1" s="21"/>
-    <row r="249" ht="15.75" customHeight="1" s="21"/>
-    <row r="250" ht="15.75" customHeight="1" s="21"/>
-    <row r="251" ht="15.75" customHeight="1" s="21"/>
-    <row r="252" ht="15.75" customHeight="1" s="21"/>
-    <row r="253" ht="15.75" customHeight="1" s="21"/>
-    <row r="254" ht="15.75" customHeight="1" s="21"/>
-    <row r="255" ht="15.75" customHeight="1" s="21"/>
-    <row r="256" ht="15.75" customHeight="1" s="21"/>
-    <row r="257" ht="15.75" customHeight="1" s="21"/>
-    <row r="258" ht="15.75" customHeight="1" s="21"/>
-    <row r="259" ht="15.75" customHeight="1" s="21"/>
-    <row r="260" ht="15.75" customHeight="1" s="21"/>
-    <row r="261" ht="15.75" customHeight="1" s="21"/>
-    <row r="262" ht="15.75" customHeight="1" s="21"/>
-    <row r="263" ht="15.75" customHeight="1" s="21"/>
-    <row r="264" ht="15.75" customHeight="1" s="21"/>
-    <row r="265" ht="15.75" customHeight="1" s="21"/>
-    <row r="266" ht="15.75" customHeight="1" s="21"/>
-    <row r="267" ht="15.75" customHeight="1" s="21"/>
-    <row r="268" ht="15.75" customHeight="1" s="21"/>
-    <row r="269" ht="15.75" customHeight="1" s="21"/>
-    <row r="270" ht="15.75" customHeight="1" s="21"/>
-    <row r="271" ht="15.75" customHeight="1" s="21"/>
-    <row r="272" ht="15.75" customHeight="1" s="21"/>
-    <row r="273" ht="15.75" customHeight="1" s="21"/>
-    <row r="274" ht="15.75" customHeight="1" s="21"/>
-    <row r="275" ht="15.75" customHeight="1" s="21"/>
-    <row r="276" ht="15.75" customHeight="1" s="21"/>
-    <row r="277" ht="15.75" customHeight="1" s="21"/>
-    <row r="278" ht="15.75" customHeight="1" s="21"/>
-    <row r="279" ht="15.75" customHeight="1" s="21"/>
-    <row r="280" ht="15.75" customHeight="1" s="21"/>
-    <row r="281" ht="15.75" customHeight="1" s="21"/>
-    <row r="282" ht="15.75" customHeight="1" s="21"/>
-    <row r="283" ht="15.75" customHeight="1" s="21"/>
-    <row r="284" ht="15.75" customHeight="1" s="21"/>
-    <row r="285" ht="15.75" customHeight="1" s="21"/>
-    <row r="286" ht="15.75" customHeight="1" s="21"/>
-    <row r="287" ht="15.75" customHeight="1" s="21"/>
-    <row r="288" ht="15.75" customHeight="1" s="21"/>
-    <row r="289" ht="15.75" customHeight="1" s="21"/>
-    <row r="290" ht="15.75" customHeight="1" s="21"/>
-    <row r="291" ht="15.75" customHeight="1" s="21"/>
-    <row r="292" ht="15.75" customHeight="1" s="21"/>
-    <row r="293" ht="15.75" customHeight="1" s="21"/>
-    <row r="294" ht="15.75" customHeight="1" s="21"/>
-    <row r="295" ht="15.75" customHeight="1" s="21"/>
-    <row r="296" ht="15.75" customHeight="1" s="21"/>
-    <row r="297" ht="15.75" customHeight="1" s="21"/>
-    <row r="298" ht="15.75" customHeight="1" s="21"/>
-    <row r="299" ht="15.75" customHeight="1" s="21"/>
-    <row r="300" ht="15.75" customHeight="1" s="21"/>
-    <row r="301" ht="15.75" customHeight="1" s="21"/>
-    <row r="302" ht="15.75" customHeight="1" s="21"/>
-    <row r="303" ht="15.75" customHeight="1" s="21"/>
-    <row r="304" ht="15.75" customHeight="1" s="21"/>
-    <row r="305" ht="15.75" customHeight="1" s="21"/>
-    <row r="306" ht="15.75" customHeight="1" s="21"/>
-    <row r="307" ht="15.75" customHeight="1" s="21"/>
-    <row r="308" ht="15.75" customHeight="1" s="21"/>
-    <row r="309" ht="15.75" customHeight="1" s="21"/>
-    <row r="310" ht="15.75" customHeight="1" s="21"/>
-    <row r="311" ht="15.75" customHeight="1" s="21"/>
-    <row r="312" ht="15.75" customHeight="1" s="21"/>
-    <row r="313" ht="15.75" customHeight="1" s="21"/>
-    <row r="314" ht="15.75" customHeight="1" s="21"/>
-    <row r="315" ht="15.75" customHeight="1" s="21"/>
-    <row r="316" ht="15.75" customHeight="1" s="21"/>
-    <row r="317" ht="15.75" customHeight="1" s="21"/>
-    <row r="318" ht="15.75" customHeight="1" s="21"/>
-    <row r="319" ht="15.75" customHeight="1" s="21"/>
-    <row r="320" ht="15.75" customHeight="1" s="21"/>
-    <row r="321" ht="15.75" customHeight="1" s="21"/>
-    <row r="322" ht="15.75" customHeight="1" s="21"/>
-    <row r="323" ht="15.75" customHeight="1" s="21"/>
-    <row r="324" ht="15.75" customHeight="1" s="21"/>
-    <row r="325" ht="15.75" customHeight="1" s="21"/>
-    <row r="326" ht="15.75" customHeight="1" s="21"/>
-    <row r="327" ht="15.75" customHeight="1" s="21"/>
-    <row r="328" ht="15.75" customHeight="1" s="21"/>
-    <row r="329" ht="15.75" customHeight="1" s="21"/>
-    <row r="330" ht="15.75" customHeight="1" s="21"/>
-    <row r="331" ht="15.75" customHeight="1" s="21"/>
-    <row r="332" ht="15.75" customHeight="1" s="21"/>
-    <row r="333" ht="15.75" customHeight="1" s="21"/>
-    <row r="334" ht="15.75" customHeight="1" s="21"/>
-    <row r="335" ht="15.75" customHeight="1" s="21"/>
-    <row r="336" ht="15.75" customHeight="1" s="21"/>
-    <row r="337" ht="15.75" customHeight="1" s="21"/>
-    <row r="338" ht="15.75" customHeight="1" s="21"/>
-    <row r="339" ht="15.75" customHeight="1" s="21"/>
-    <row r="340" ht="15.75" customHeight="1" s="21"/>
-    <row r="341" ht="15.75" customHeight="1" s="21"/>
-    <row r="342" ht="15.75" customHeight="1" s="21"/>
-    <row r="343" ht="15.75" customHeight="1" s="21"/>
-    <row r="344" ht="15.75" customHeight="1" s="21"/>
-    <row r="345" ht="15.75" customHeight="1" s="21"/>
-    <row r="346" ht="15.75" customHeight="1" s="21"/>
-    <row r="347" ht="15.75" customHeight="1" s="21"/>
-    <row r="348" ht="15.75" customHeight="1" s="21"/>
-    <row r="349" ht="15.75" customHeight="1" s="21"/>
-    <row r="350" ht="15.75" customHeight="1" s="21"/>
-    <row r="351" ht="15.75" customHeight="1" s="21"/>
-    <row r="352" ht="15.75" customHeight="1" s="21"/>
-    <row r="353" ht="15.75" customHeight="1" s="21"/>
-    <row r="354" ht="15.75" customHeight="1" s="21"/>
-    <row r="355" ht="15.75" customHeight="1" s="21"/>
-    <row r="356" ht="15.75" customHeight="1" s="21"/>
-    <row r="357" ht="15.75" customHeight="1" s="21"/>
-    <row r="358" ht="15.75" customHeight="1" s="21"/>
-    <row r="359" ht="15.75" customHeight="1" s="21"/>
-    <row r="360" ht="15.75" customHeight="1" s="21"/>
-    <row r="361" ht="15.75" customHeight="1" s="21"/>
-    <row r="362" ht="15.75" customHeight="1" s="21"/>
-    <row r="363" ht="15.75" customHeight="1" s="21"/>
-    <row r="364" ht="15.75" customHeight="1" s="21"/>
-    <row r="365" ht="15.75" customHeight="1" s="21"/>
-    <row r="366" ht="15.75" customHeight="1" s="21"/>
-    <row r="367" ht="15.75" customHeight="1" s="21"/>
-    <row r="368" ht="15.75" customHeight="1" s="21"/>
-    <row r="369" ht="15.75" customHeight="1" s="21"/>
-    <row r="370" ht="15.75" customHeight="1" s="21"/>
-    <row r="371" ht="15.75" customHeight="1" s="21"/>
-    <row r="372" ht="15.75" customHeight="1" s="21"/>
-    <row r="373" ht="15.75" customHeight="1" s="21"/>
-    <row r="374" ht="15.75" customHeight="1" s="21"/>
-    <row r="375" ht="15.75" customHeight="1" s="21"/>
-    <row r="376" ht="15.75" customHeight="1" s="21"/>
-    <row r="377" ht="15.75" customHeight="1" s="21"/>
-    <row r="378" ht="15.75" customHeight="1" s="21"/>
-    <row r="379" ht="15.75" customHeight="1" s="21"/>
-    <row r="380" ht="15.75" customHeight="1" s="21"/>
-    <row r="381" ht="15.75" customHeight="1" s="21"/>
-    <row r="382" ht="15.75" customHeight="1" s="21"/>
-    <row r="383" ht="15.75" customHeight="1" s="21"/>
-    <row r="384" ht="15.75" customHeight="1" s="21"/>
-    <row r="385" ht="15.75" customHeight="1" s="21"/>
-    <row r="386" ht="15.75" customHeight="1" s="21"/>
-    <row r="387" ht="15.75" customHeight="1" s="21"/>
-    <row r="388" ht="15.75" customHeight="1" s="21"/>
-    <row r="389" ht="15.75" customHeight="1" s="21"/>
-    <row r="390" ht="15.75" customHeight="1" s="21"/>
-    <row r="391" ht="15.75" customHeight="1" s="21"/>
-    <row r="392" ht="15.75" customHeight="1" s="21"/>
-    <row r="393" ht="15.75" customHeight="1" s="21"/>
-    <row r="394" ht="15.75" customHeight="1" s="21"/>
-    <row r="395" ht="15.75" customHeight="1" s="21"/>
-    <row r="396" ht="15.75" customHeight="1" s="21"/>
-    <row r="397" ht="15.75" customHeight="1" s="21"/>
-    <row r="398" ht="15.75" customHeight="1" s="21"/>
-    <row r="399" ht="15.75" customHeight="1" s="21"/>
-    <row r="400" ht="15.75" customHeight="1" s="21"/>
-    <row r="401" ht="15.75" customHeight="1" s="21"/>
-    <row r="402" ht="15.75" customHeight="1" s="21"/>
-    <row r="403" ht="15.75" customHeight="1" s="21"/>
-    <row r="404" ht="15.75" customHeight="1" s="21"/>
-    <row r="405" ht="15.75" customHeight="1" s="21"/>
-    <row r="406" ht="15.75" customHeight="1" s="21"/>
-    <row r="407" ht="15.75" customHeight="1" s="21"/>
-    <row r="408" ht="15.75" customHeight="1" s="21"/>
-    <row r="409" ht="15.75" customHeight="1" s="21"/>
-    <row r="410" ht="15.75" customHeight="1" s="21"/>
-    <row r="411" ht="15.75" customHeight="1" s="21"/>
-    <row r="412" ht="15.75" customHeight="1" s="21"/>
-    <row r="413" ht="15.75" customHeight="1" s="21"/>
-    <row r="414" ht="15.75" customHeight="1" s="21"/>
-    <row r="415" ht="15.75" customHeight="1" s="21"/>
-    <row r="416" ht="15.75" customHeight="1" s="21"/>
-    <row r="417" ht="15.75" customHeight="1" s="21"/>
-    <row r="418" ht="15.75" customHeight="1" s="21"/>
-    <row r="419" ht="15.75" customHeight="1" s="21"/>
-    <row r="420" ht="15.75" customHeight="1" s="21"/>
-    <row r="421" ht="15.75" customHeight="1" s="21"/>
-    <row r="422" ht="15.75" customHeight="1" s="21"/>
-    <row r="423" ht="15.75" customHeight="1" s="21"/>
-    <row r="424" ht="15.75" customHeight="1" s="21"/>
-    <row r="425" ht="15.75" customHeight="1" s="21"/>
-    <row r="426" ht="15.75" customHeight="1" s="21"/>
-    <row r="427" ht="15.75" customHeight="1" s="21"/>
-    <row r="428" ht="15.75" customHeight="1" s="21"/>
-    <row r="429" ht="15.75" customHeight="1" s="21"/>
-    <row r="430" ht="15.75" customHeight="1" s="21"/>
-    <row r="431" ht="15.75" customHeight="1" s="21"/>
-    <row r="432" ht="15.75" customHeight="1" s="21"/>
-    <row r="433" ht="15.75" customHeight="1" s="21"/>
-    <row r="434" ht="15.75" customHeight="1" s="21"/>
-    <row r="435" ht="15.75" customHeight="1" s="21"/>
-    <row r="436" ht="15.75" customHeight="1" s="21"/>
-    <row r="437" ht="15.75" customHeight="1" s="21"/>
-    <row r="438" ht="15.75" customHeight="1" s="21"/>
-    <row r="439" ht="15.75" customHeight="1" s="21"/>
-    <row r="440" ht="15.75" customHeight="1" s="21"/>
-    <row r="441" ht="15.75" customHeight="1" s="21"/>
-    <row r="442" ht="15.75" customHeight="1" s="21"/>
-    <row r="443" ht="15.75" customHeight="1" s="21"/>
-    <row r="444" ht="15.75" customHeight="1" s="21"/>
-    <row r="445" ht="15.75" customHeight="1" s="21"/>
-    <row r="446" ht="15.75" customHeight="1" s="21"/>
-    <row r="447" ht="15.75" customHeight="1" s="21"/>
-    <row r="448" ht="15.75" customHeight="1" s="21"/>
-    <row r="449" ht="15.75" customHeight="1" s="21"/>
-    <row r="450" ht="15.75" customHeight="1" s="21"/>
-    <row r="451" ht="15.75" customHeight="1" s="21"/>
-    <row r="452" ht="15.75" customHeight="1" s="21"/>
-    <row r="453" ht="15.75" customHeight="1" s="21"/>
-    <row r="454" ht="15.75" customHeight="1" s="21"/>
-    <row r="455" ht="15.75" customHeight="1" s="21"/>
-    <row r="456" ht="15.75" customHeight="1" s="21"/>
-    <row r="457" ht="15.75" customHeight="1" s="21"/>
-    <row r="458" ht="15.75" customHeight="1" s="21"/>
-    <row r="459" ht="15.75" customHeight="1" s="21"/>
-    <row r="460" ht="15.75" customHeight="1" s="21"/>
-    <row r="461" ht="15.75" customHeight="1" s="21"/>
-    <row r="462" ht="15.75" customHeight="1" s="21"/>
-    <row r="463" ht="15.75" customHeight="1" s="21"/>
-    <row r="464" ht="15.75" customHeight="1" s="21"/>
-    <row r="465" ht="15.75" customHeight="1" s="21"/>
-    <row r="466" ht="15.75" customHeight="1" s="21"/>
-    <row r="467" ht="15.75" customHeight="1" s="21"/>
-    <row r="468" ht="15.75" customHeight="1" s="21"/>
-    <row r="469" ht="15.75" customHeight="1" s="21"/>
-    <row r="470" ht="15.75" customHeight="1" s="21"/>
-    <row r="471" ht="15.75" customHeight="1" s="21"/>
-    <row r="472" ht="15.75" customHeight="1" s="21"/>
-    <row r="473" ht="15.75" customHeight="1" s="21"/>
-    <row r="474" ht="15.75" customHeight="1" s="21"/>
-    <row r="475" ht="15.75" customHeight="1" s="21"/>
-    <row r="476" ht="15.75" customHeight="1" s="21"/>
-    <row r="477" ht="15.75" customHeight="1" s="21"/>
-    <row r="478" ht="15.75" customHeight="1" s="21"/>
-    <row r="479" ht="15.75" customHeight="1" s="21"/>
-    <row r="480" ht="15.75" customHeight="1" s="21"/>
-    <row r="481" ht="15.75" customHeight="1" s="21"/>
-    <row r="482" ht="15.75" customHeight="1" s="21"/>
-    <row r="483" ht="15.75" customHeight="1" s="21"/>
-    <row r="484" ht="15.75" customHeight="1" s="21"/>
-    <row r="485" ht="15.75" customHeight="1" s="21"/>
-    <row r="486" ht="15.75" customHeight="1" s="21"/>
-    <row r="487" ht="15.75" customHeight="1" s="21"/>
-    <row r="488" ht="15.75" customHeight="1" s="21"/>
-    <row r="489" ht="15.75" customHeight="1" s="21"/>
-    <row r="490" ht="15.75" customHeight="1" s="21"/>
-    <row r="491" ht="15.75" customHeight="1" s="21"/>
-    <row r="492" ht="15.75" customHeight="1" s="21"/>
-    <row r="493" ht="15.75" customHeight="1" s="21"/>
-    <row r="494" ht="15.75" customHeight="1" s="21"/>
-    <row r="495" ht="15.75" customHeight="1" s="21"/>
-    <row r="496" ht="15.75" customHeight="1" s="21"/>
-    <row r="497" ht="15.75" customHeight="1" s="21"/>
-    <row r="498" ht="15.75" customHeight="1" s="21"/>
-    <row r="499" ht="15.75" customHeight="1" s="21"/>
-    <row r="500" ht="15.75" customHeight="1" s="21"/>
-    <row r="501" ht="15.75" customHeight="1" s="21"/>
-    <row r="502" ht="15.75" customHeight="1" s="21"/>
-    <row r="503" ht="15.75" customHeight="1" s="21"/>
-    <row r="504" ht="15.75" customHeight="1" s="21"/>
-    <row r="505" ht="15.75" customHeight="1" s="21"/>
-    <row r="506" ht="15.75" customHeight="1" s="21"/>
-    <row r="507" ht="15.75" customHeight="1" s="21"/>
-    <row r="508" ht="15.75" customHeight="1" s="21"/>
-    <row r="509" ht="15.75" customHeight="1" s="21"/>
-    <row r="510" ht="15.75" customHeight="1" s="21"/>
-    <row r="511" ht="15.75" customHeight="1" s="21"/>
-    <row r="512" ht="15.75" customHeight="1" s="21"/>
-    <row r="513" ht="15.75" customHeight="1" s="21"/>
-    <row r="514" ht="15.75" customHeight="1" s="21"/>
-    <row r="515" ht="15.75" customHeight="1" s="21"/>
-    <row r="516" ht="15.75" customHeight="1" s="21"/>
-    <row r="517" ht="15.75" customHeight="1" s="21"/>
-    <row r="518" ht="15.75" customHeight="1" s="21"/>
-    <row r="519" ht="15.75" customHeight="1" s="21"/>
-    <row r="520" ht="15.75" customHeight="1" s="21"/>
-    <row r="521" ht="15.75" customHeight="1" s="21"/>
-    <row r="522" ht="15.75" customHeight="1" s="21"/>
-    <row r="523" ht="15.75" customHeight="1" s="21"/>
-    <row r="524" ht="15.75" customHeight="1" s="21"/>
-    <row r="525" ht="15.75" customHeight="1" s="21"/>
-    <row r="526" ht="15.75" customHeight="1" s="21"/>
-    <row r="527" ht="15.75" customHeight="1" s="21"/>
-    <row r="528" ht="15.75" customHeight="1" s="21"/>
-    <row r="529" ht="15.75" customHeight="1" s="21"/>
-    <row r="530" ht="15.75" customHeight="1" s="21"/>
-    <row r="531" ht="15.75" customHeight="1" s="21"/>
-    <row r="532" ht="15.75" customHeight="1" s="21"/>
-    <row r="533" ht="15.75" customHeight="1" s="21"/>
-    <row r="534" ht="15.75" customHeight="1" s="21"/>
-    <row r="535" ht="15.75" customHeight="1" s="21"/>
-    <row r="536" ht="15.75" customHeight="1" s="21"/>
-    <row r="537" ht="15.75" customHeight="1" s="21"/>
-    <row r="538" ht="15.75" customHeight="1" s="21"/>
-    <row r="539" ht="15.75" customHeight="1" s="21"/>
-    <row r="540" ht="15.75" customHeight="1" s="21"/>
-    <row r="541" ht="15.75" customHeight="1" s="21"/>
-    <row r="542" ht="15.75" customHeight="1" s="21"/>
-    <row r="543" ht="15.75" customHeight="1" s="21"/>
-    <row r="544" ht="15.75" customHeight="1" s="21"/>
-    <row r="545" ht="15.75" customHeight="1" s="21"/>
-    <row r="546" ht="15.75" customHeight="1" s="21"/>
-    <row r="547" ht="15.75" customHeight="1" s="21"/>
-    <row r="548" ht="15.75" customHeight="1" s="21"/>
-    <row r="549" ht="15.75" customHeight="1" s="21"/>
-    <row r="550" ht="15.75" customHeight="1" s="21"/>
-    <row r="551" ht="15.75" customHeight="1" s="21"/>
-    <row r="552" ht="15.75" customHeight="1" s="21"/>
-    <row r="553" ht="15.75" customHeight="1" s="21"/>
-    <row r="554" ht="15.75" customHeight="1" s="21"/>
-    <row r="555" ht="15.75" customHeight="1" s="21"/>
-    <row r="556" ht="15.75" customHeight="1" s="21"/>
-    <row r="557" ht="15.75" customHeight="1" s="21"/>
-    <row r="558" ht="15.75" customHeight="1" s="21"/>
-    <row r="559" ht="15.75" customHeight="1" s="21"/>
-    <row r="560" ht="15.75" customHeight="1" s="21"/>
-    <row r="561" ht="15.75" customHeight="1" s="21"/>
-    <row r="562" ht="15.75" customHeight="1" s="21"/>
-    <row r="563" ht="15.75" customHeight="1" s="21"/>
-    <row r="564" ht="15.75" customHeight="1" s="21"/>
-    <row r="565" ht="15.75" customHeight="1" s="21"/>
-    <row r="566" ht="15.75" customHeight="1" s="21"/>
-    <row r="567" ht="15.75" customHeight="1" s="21"/>
-    <row r="568" ht="15.75" customHeight="1" s="21"/>
-    <row r="569" ht="15.75" customHeight="1" s="21"/>
-    <row r="570" ht="15.75" customHeight="1" s="21"/>
-    <row r="571" ht="15.75" customHeight="1" s="21"/>
-    <row r="572" ht="15.75" customHeight="1" s="21"/>
-    <row r="573" ht="15.75" customHeight="1" s="21"/>
-    <row r="574" ht="15.75" customHeight="1" s="21"/>
-    <row r="575" ht="15.75" customHeight="1" s="21"/>
-    <row r="576" ht="15.75" customHeight="1" s="21"/>
-    <row r="577" ht="15.75" customHeight="1" s="21"/>
-    <row r="578" ht="15.75" customHeight="1" s="21"/>
-    <row r="579" ht="15.75" customHeight="1" s="21"/>
-    <row r="580" ht="15.75" customHeight="1" s="21"/>
-    <row r="581" ht="15.75" customHeight="1" s="21"/>
-    <row r="582" ht="15.75" customHeight="1" s="21"/>
-    <row r="583" ht="15.75" customHeight="1" s="21"/>
-    <row r="584" ht="15.75" customHeight="1" s="21"/>
-    <row r="585" ht="15.75" customHeight="1" s="21"/>
-    <row r="586" ht="15.75" customHeight="1" s="21"/>
-    <row r="587" ht="15.75" customHeight="1" s="21"/>
-    <row r="588" ht="15.75" customHeight="1" s="21"/>
-    <row r="589" ht="15.75" customHeight="1" s="21"/>
-    <row r="590" ht="15.75" customHeight="1" s="21"/>
-    <row r="591" ht="15.75" customHeight="1" s="21"/>
-    <row r="592" ht="15.75" customHeight="1" s="21"/>
-    <row r="593" ht="15.75" customHeight="1" s="21"/>
-    <row r="594" ht="15.75" customHeight="1" s="21"/>
-    <row r="595" ht="15.75" customHeight="1" s="21"/>
-    <row r="596" ht="15.75" customHeight="1" s="21"/>
-    <row r="597" ht="15.75" customHeight="1" s="21"/>
-    <row r="598" ht="15.75" customHeight="1" s="21"/>
-    <row r="599" ht="15.75" customHeight="1" s="21"/>
-    <row r="600" ht="15.75" customHeight="1" s="21"/>
-    <row r="601" ht="15.75" customHeight="1" s="21"/>
-    <row r="602" ht="15.75" customHeight="1" s="21"/>
-    <row r="603" ht="15.75" customHeight="1" s="21"/>
-    <row r="604" ht="15.75" customHeight="1" s="21"/>
-    <row r="605" ht="15.75" customHeight="1" s="21"/>
-    <row r="606" ht="15.75" customHeight="1" s="21"/>
-    <row r="607" ht="15.75" customHeight="1" s="21"/>
-    <row r="608" ht="15.75" customHeight="1" s="21"/>
-    <row r="609" ht="15.75" customHeight="1" s="21"/>
-    <row r="610" ht="15.75" customHeight="1" s="21"/>
-    <row r="611" ht="15.75" customHeight="1" s="21"/>
-    <row r="612" ht="15.75" customHeight="1" s="21"/>
-    <row r="613" ht="15.75" customHeight="1" s="21"/>
-    <row r="614" ht="15.75" customHeight="1" s="21"/>
-    <row r="615" ht="15.75" customHeight="1" s="21"/>
-    <row r="616" ht="15.75" customHeight="1" s="21"/>
-    <row r="617" ht="15.75" customHeight="1" s="21"/>
-    <row r="618" ht="15.75" customHeight="1" s="21"/>
-    <row r="619" ht="15.75" customHeight="1" s="21"/>
-    <row r="620" ht="15.75" customHeight="1" s="21"/>
-    <row r="621" ht="15.75" customHeight="1" s="21"/>
-    <row r="622" ht="15.75" customHeight="1" s="21"/>
-    <row r="623" ht="15.75" customHeight="1" s="21"/>
-    <row r="624" ht="15.75" customHeight="1" s="21"/>
-    <row r="625" ht="15.75" customHeight="1" s="21"/>
-    <row r="626" ht="15.75" customHeight="1" s="21"/>
-    <row r="627" ht="15.75" customHeight="1" s="21"/>
-    <row r="628" ht="15.75" customHeight="1" s="21"/>
-    <row r="629" ht="15.75" customHeight="1" s="21"/>
-    <row r="630" ht="15.75" customHeight="1" s="21"/>
-    <row r="631" ht="15.75" customHeight="1" s="21"/>
-    <row r="632" ht="15.75" customHeight="1" s="21"/>
-    <row r="633" ht="15.75" customHeight="1" s="21"/>
-    <row r="634" ht="15.75" customHeight="1" s="21"/>
-    <row r="635" ht="15.75" customHeight="1" s="21"/>
-    <row r="636" ht="15.75" customHeight="1" s="21"/>
-    <row r="637" ht="15.75" customHeight="1" s="21"/>
-    <row r="638" ht="15.75" customHeight="1" s="21"/>
-    <row r="639" ht="15.75" customHeight="1" s="21"/>
-    <row r="640" ht="15.75" customHeight="1" s="21"/>
-    <row r="641" ht="15.75" customHeight="1" s="21"/>
-    <row r="642" ht="15.75" customHeight="1" s="21"/>
-    <row r="643" ht="15.75" customHeight="1" s="21"/>
-    <row r="644" ht="15.75" customHeight="1" s="21"/>
-    <row r="645" ht="15.75" customHeight="1" s="21"/>
-    <row r="646" ht="15.75" customHeight="1" s="21"/>
-    <row r="647" ht="15.75" customHeight="1" s="21"/>
-    <row r="648" ht="15.75" customHeight="1" s="21"/>
-    <row r="649" ht="15.75" customHeight="1" s="21"/>
-    <row r="650" ht="15.75" customHeight="1" s="21"/>
-    <row r="651" ht="15.75" customHeight="1" s="21"/>
-    <row r="652" ht="15.75" customHeight="1" s="21"/>
-    <row r="653" ht="15.75" customHeight="1" s="21"/>
-    <row r="654" ht="15.75" customHeight="1" s="21"/>
-    <row r="655" ht="15.75" customHeight="1" s="21"/>
-    <row r="656" ht="15.75" customHeight="1" s="21"/>
-    <row r="657" ht="15.75" customHeight="1" s="21"/>
-    <row r="658" ht="15.75" customHeight="1" s="21"/>
-    <row r="659" ht="15.75" customHeight="1" s="21"/>
-    <row r="660" ht="15.75" customHeight="1" s="21"/>
-    <row r="661" ht="15.75" customHeight="1" s="21"/>
-    <row r="662" ht="15.75" customHeight="1" s="21"/>
-    <row r="663" ht="15.75" customHeight="1" s="21"/>
-    <row r="664" ht="15.75" customHeight="1" s="21"/>
-    <row r="665" ht="15.75" customHeight="1" s="21"/>
-    <row r="666" ht="15.75" customHeight="1" s="21"/>
-    <row r="667" ht="15.75" customHeight="1" s="21"/>
-    <row r="668" ht="15.75" customHeight="1" s="21"/>
-    <row r="669" ht="15.75" customHeight="1" s="21"/>
-    <row r="670" ht="15.75" customHeight="1" s="21"/>
-    <row r="671" ht="15.75" customHeight="1" s="21"/>
-    <row r="672" ht="15.75" customHeight="1" s="21"/>
-    <row r="673" ht="15.75" customHeight="1" s="21"/>
-    <row r="674" ht="15.75" customHeight="1" s="21"/>
-    <row r="675" ht="15.75" customHeight="1" s="21"/>
-    <row r="676" ht="15.75" customHeight="1" s="21"/>
-    <row r="677" ht="15.75" customHeight="1" s="21"/>
-    <row r="678" ht="15.75" customHeight="1" s="21"/>
-    <row r="679" ht="15.75" customHeight="1" s="21"/>
-    <row r="680" ht="15.75" customHeight="1" s="21"/>
-    <row r="681" ht="15.75" customHeight="1" s="21"/>
-    <row r="682" ht="15.75" customHeight="1" s="21"/>
-    <row r="683" ht="15.75" customHeight="1" s="21"/>
-    <row r="684" ht="15.75" customHeight="1" s="21"/>
-    <row r="685" ht="15.75" customHeight="1" s="21"/>
-    <row r="686" ht="15.75" customHeight="1" s="21"/>
-    <row r="687" ht="15.75" customHeight="1" s="21"/>
-    <row r="688" ht="15.75" customHeight="1" s="21"/>
-    <row r="689" ht="15.75" customHeight="1" s="21"/>
-    <row r="690" ht="15.75" customHeight="1" s="21"/>
-    <row r="691" ht="15.75" customHeight="1" s="21"/>
-    <row r="692" ht="15.75" customHeight="1" s="21"/>
-    <row r="693" ht="15.75" customHeight="1" s="21"/>
-    <row r="694" ht="15.75" customHeight="1" s="21"/>
-    <row r="695" ht="15.75" customHeight="1" s="21"/>
-    <row r="696" ht="15.75" customHeight="1" s="21"/>
-    <row r="697" ht="15.75" customHeight="1" s="21"/>
-    <row r="698" ht="15.75" customHeight="1" s="21"/>
-    <row r="699" ht="15.75" customHeight="1" s="21"/>
-    <row r="700" ht="15.75" customHeight="1" s="21"/>
-    <row r="701" ht="15.75" customHeight="1" s="21"/>
-    <row r="702" ht="15.75" customHeight="1" s="21"/>
-    <row r="703" ht="15.75" customHeight="1" s="21"/>
-    <row r="704" ht="15.75" customHeight="1" s="21"/>
-    <row r="705" ht="15.75" customHeight="1" s="21"/>
-    <row r="706" ht="15.75" customHeight="1" s="21"/>
-    <row r="707" ht="15.75" customHeight="1" s="21"/>
-    <row r="708" ht="15.75" customHeight="1" s="21"/>
-    <row r="709" ht="15.75" customHeight="1" s="21"/>
-    <row r="710" ht="15.75" customHeight="1" s="21"/>
-    <row r="711" ht="15.75" customHeight="1" s="21"/>
-    <row r="712" ht="15.75" customHeight="1" s="21"/>
-    <row r="713" ht="15.75" customHeight="1" s="21"/>
-    <row r="714" ht="15.75" customHeight="1" s="21"/>
-    <row r="715" ht="15.75" customHeight="1" s="21"/>
-    <row r="716" ht="15.75" customHeight="1" s="21"/>
-    <row r="717" ht="15.75" customHeight="1" s="21"/>
-    <row r="718" ht="15.75" customHeight="1" s="21"/>
-    <row r="719" ht="15.75" customHeight="1" s="21"/>
-    <row r="720" ht="15.75" customHeight="1" s="21"/>
-    <row r="721" ht="15.75" customHeight="1" s="21"/>
-    <row r="722" ht="15.75" customHeight="1" s="21"/>
-    <row r="723" ht="15.75" customHeight="1" s="21"/>
-    <row r="724" ht="15.75" customHeight="1" s="21"/>
-    <row r="725" ht="15.75" customHeight="1" s="21"/>
-    <row r="726" ht="15.75" customHeight="1" s="21"/>
-    <row r="727" ht="15.75" customHeight="1" s="21"/>
-    <row r="728" ht="15.75" customHeight="1" s="21"/>
-    <row r="729" ht="15.75" customHeight="1" s="21"/>
-    <row r="730" ht="15.75" customHeight="1" s="21"/>
-    <row r="731" ht="15.75" customHeight="1" s="21"/>
-    <row r="732" ht="15.75" customHeight="1" s="21"/>
-    <row r="733" ht="15.75" customHeight="1" s="21"/>
-    <row r="734" ht="15.75" customHeight="1" s="21"/>
-    <row r="735" ht="15.75" customHeight="1" s="21"/>
-    <row r="736" ht="15.75" customHeight="1" s="21"/>
-    <row r="737" ht="15.75" customHeight="1" s="21"/>
-    <row r="738" ht="15.75" customHeight="1" s="21"/>
-    <row r="739" ht="15.75" customHeight="1" s="21"/>
-    <row r="740" ht="15.75" customHeight="1" s="21"/>
-    <row r="741" ht="15.75" customHeight="1" s="21"/>
-    <row r="742" ht="15.75" customHeight="1" s="21"/>
-    <row r="743" ht="15.75" customHeight="1" s="21"/>
-    <row r="744" ht="15.75" customHeight="1" s="21"/>
-    <row r="745" ht="15.75" customHeight="1" s="21"/>
-    <row r="746" ht="15.75" customHeight="1" s="21"/>
-    <row r="747" ht="15.75" customHeight="1" s="21"/>
-    <row r="748" ht="15.75" customHeight="1" s="21"/>
-    <row r="749" ht="15.75" customHeight="1" s="21"/>
-    <row r="750" ht="15.75" customHeight="1" s="21"/>
-    <row r="751" ht="15.75" customHeight="1" s="21"/>
-    <row r="752" ht="15.75" customHeight="1" s="21"/>
-    <row r="753" ht="15.75" customHeight="1" s="21"/>
-    <row r="754" ht="15.75" customHeight="1" s="21"/>
-    <row r="755" ht="15.75" customHeight="1" s="21"/>
-    <row r="756" ht="15.75" customHeight="1" s="21"/>
-    <row r="757" ht="15.75" customHeight="1" s="21"/>
-    <row r="758" ht="15.75" customHeight="1" s="21"/>
-    <row r="759" ht="15.75" customHeight="1" s="21"/>
-    <row r="760" ht="15.75" customHeight="1" s="21"/>
-    <row r="761" ht="15.75" customHeight="1" s="21"/>
-    <row r="762" ht="15.75" customHeight="1" s="21"/>
-    <row r="763" ht="15.75" customHeight="1" s="21"/>
-    <row r="764" ht="15.75" customHeight="1" s="21"/>
-    <row r="765" ht="15.75" customHeight="1" s="21"/>
-    <row r="766" ht="15.75" customHeight="1" s="21"/>
-    <row r="767" ht="15.75" customHeight="1" s="21"/>
-    <row r="768" ht="15.75" customHeight="1" s="21"/>
-    <row r="769" ht="15.75" customHeight="1" s="21"/>
-    <row r="770" ht="15.75" customHeight="1" s="21"/>
-    <row r="771" ht="15.75" customHeight="1" s="21"/>
-    <row r="772" ht="15.75" customHeight="1" s="21"/>
-    <row r="773" ht="15.75" customHeight="1" s="21"/>
-    <row r="774" ht="15.75" customHeight="1" s="21"/>
-    <row r="775" ht="15.75" customHeight="1" s="21"/>
-    <row r="776" ht="15.75" customHeight="1" s="21"/>
-    <row r="777" ht="15.75" customHeight="1" s="21"/>
-    <row r="778" ht="15.75" customHeight="1" s="21"/>
-    <row r="779" ht="15.75" customHeight="1" s="21"/>
-    <row r="780" ht="15.75" customHeight="1" s="21"/>
-    <row r="781" ht="15.75" customHeight="1" s="21"/>
-    <row r="782" ht="15.75" customHeight="1" s="21"/>
-    <row r="783" ht="15.75" customHeight="1" s="21"/>
-    <row r="784" ht="15.75" customHeight="1" s="21"/>
-    <row r="785" ht="15.75" customHeight="1" s="21"/>
-    <row r="786" ht="15.75" customHeight="1" s="21"/>
-    <row r="787" ht="15.75" customHeight="1" s="21"/>
-    <row r="788" ht="15.75" customHeight="1" s="21"/>
-    <row r="789" ht="15.75" customHeight="1" s="21"/>
-    <row r="790" ht="15.75" customHeight="1" s="21"/>
-    <row r="791" ht="15.75" customHeight="1" s="21"/>
-    <row r="792" ht="15.75" customHeight="1" s="21"/>
-    <row r="793" ht="15.75" customHeight="1" s="21"/>
-    <row r="794" ht="15.75" customHeight="1" s="21"/>
-    <row r="795" ht="15.75" customHeight="1" s="21"/>
-    <row r="796" ht="15.75" customHeight="1" s="21"/>
-    <row r="797" ht="15.75" customHeight="1" s="21"/>
-    <row r="798" ht="15.75" customHeight="1" s="21"/>
-    <row r="799" ht="15.75" customHeight="1" s="21"/>
-    <row r="800" ht="15.75" customHeight="1" s="21"/>
-    <row r="801" ht="15.75" customHeight="1" s="21"/>
-    <row r="802" ht="15.75" customHeight="1" s="21"/>
-    <row r="803" ht="15.75" customHeight="1" s="21"/>
-    <row r="804" ht="15.75" customHeight="1" s="21"/>
-    <row r="805" ht="15.75" customHeight="1" s="21"/>
-    <row r="806" ht="15.75" customHeight="1" s="21"/>
-    <row r="807" ht="15.75" customHeight="1" s="21"/>
-    <row r="808" ht="15.75" customHeight="1" s="21"/>
-    <row r="809" ht="15.75" customHeight="1" s="21"/>
-    <row r="810" ht="15.75" customHeight="1" s="21"/>
-    <row r="811" ht="15.75" customHeight="1" s="21"/>
-    <row r="812" ht="15.75" customHeight="1" s="21"/>
-    <row r="813" ht="15.75" customHeight="1" s="21"/>
-    <row r="814" ht="15.75" customHeight="1" s="21"/>
-    <row r="815" ht="15.75" customHeight="1" s="21"/>
-    <row r="816" ht="15.75" customHeight="1" s="21"/>
-    <row r="817" ht="15.75" customHeight="1" s="21"/>
-    <row r="818" ht="15.75" customHeight="1" s="21"/>
-    <row r="819" ht="15.75" customHeight="1" s="21"/>
-    <row r="820" ht="15.75" customHeight="1" s="21"/>
-    <row r="821" ht="15.75" customHeight="1" s="21"/>
-    <row r="822" ht="15.75" customHeight="1" s="21"/>
-    <row r="823" ht="15.75" customHeight="1" s="21"/>
-    <row r="824" ht="15.75" customHeight="1" s="21"/>
-    <row r="825" ht="15.75" customHeight="1" s="21"/>
-    <row r="826" ht="15.75" customHeight="1" s="21"/>
-    <row r="827" ht="15.75" customHeight="1" s="21"/>
-    <row r="828" ht="15.75" customHeight="1" s="21"/>
-    <row r="829" ht="15.75" customHeight="1" s="21"/>
-    <row r="830" ht="15.75" customHeight="1" s="21"/>
-    <row r="831" ht="15.75" customHeight="1" s="21"/>
-    <row r="832" ht="15.75" customHeight="1" s="21"/>
-    <row r="833" ht="15.75" customHeight="1" s="21"/>
-    <row r="834" ht="15.75" customHeight="1" s="21"/>
-    <row r="835" ht="15.75" customHeight="1" s="21"/>
-    <row r="836" ht="15.75" customHeight="1" s="21"/>
-    <row r="837" ht="15.75" customHeight="1" s="21"/>
-    <row r="838" ht="15.75" customHeight="1" s="21"/>
-    <row r="839" ht="15.75" customHeight="1" s="21"/>
-    <row r="840" ht="15.75" customHeight="1" s="21"/>
-    <row r="841" ht="15.75" customHeight="1" s="21"/>
-    <row r="842" ht="15.75" customHeight="1" s="21"/>
-    <row r="843" ht="15.75" customHeight="1" s="21"/>
-    <row r="844" ht="15.75" customHeight="1" s="21"/>
-    <row r="845" ht="15.75" customHeight="1" s="21"/>
-    <row r="846" ht="15.75" customHeight="1" s="21"/>
-    <row r="847" ht="15.75" customHeight="1" s="21"/>
-    <row r="848" ht="15.75" customHeight="1" s="21"/>
-    <row r="849" ht="15.75" customHeight="1" s="21"/>
-    <row r="850" ht="15.75" customHeight="1" s="21"/>
-    <row r="851" ht="15.75" customHeight="1" s="21"/>
-    <row r="852" ht="15.75" customHeight="1" s="21"/>
-    <row r="853" ht="15.75" customHeight="1" s="21"/>
-    <row r="854" ht="15.75" customHeight="1" s="21"/>
-    <row r="855" ht="15.75" customHeight="1" s="21"/>
-    <row r="856" ht="15.75" customHeight="1" s="21"/>
-    <row r="857" ht="15.75" customHeight="1" s="21"/>
-    <row r="858" ht="15.75" customHeight="1" s="21"/>
-    <row r="859" ht="15.75" customHeight="1" s="21"/>
-    <row r="860" ht="15.75" customHeight="1" s="21"/>
-    <row r="861" ht="15.75" customHeight="1" s="21"/>
-    <row r="862" ht="15.75" customHeight="1" s="21"/>
-    <row r="863" ht="15.75" customHeight="1" s="21"/>
-    <row r="864" ht="15.75" customHeight="1" s="21"/>
-    <row r="865" ht="15.75" customHeight="1" s="21"/>
-    <row r="866" ht="15.75" customHeight="1" s="21"/>
-    <row r="867" ht="15.75" customHeight="1" s="21"/>
-    <row r="868" ht="15.75" customHeight="1" s="21"/>
-    <row r="869" ht="15.75" customHeight="1" s="21"/>
-    <row r="870" ht="15.75" customHeight="1" s="21"/>
-    <row r="871" ht="15.75" customHeight="1" s="21"/>
-    <row r="872" ht="15.75" customHeight="1" s="21"/>
-    <row r="873" ht="15.75" customHeight="1" s="21"/>
-    <row r="874" ht="15.75" customHeight="1" s="21"/>
-    <row r="875" ht="15.75" customHeight="1" s="21"/>
-    <row r="876" ht="15.75" customHeight="1" s="21"/>
-    <row r="877" ht="15.75" customHeight="1" s="21"/>
-    <row r="878" ht="15.75" customHeight="1" s="21"/>
-    <row r="879" ht="15.75" customHeight="1" s="21"/>
-    <row r="880" ht="15.75" customHeight="1" s="21"/>
-    <row r="881" ht="15.75" customHeight="1" s="21"/>
-    <row r="882" ht="15.75" customHeight="1" s="21"/>
-    <row r="883" ht="15.75" customHeight="1" s="21"/>
-    <row r="884" ht="15.75" customHeight="1" s="21"/>
-    <row r="885" ht="15.75" customHeight="1" s="21"/>
-    <row r="886" ht="15.75" customHeight="1" s="21"/>
-    <row r="887" ht="15.75" customHeight="1" s="21"/>
-    <row r="888" ht="15.75" customHeight="1" s="21"/>
-    <row r="889" ht="15.75" customHeight="1" s="21"/>
-    <row r="890" ht="15.75" customHeight="1" s="21"/>
-    <row r="891" ht="15.75" customHeight="1" s="21"/>
-    <row r="892" ht="15.75" customHeight="1" s="21"/>
-    <row r="893" ht="15.75" customHeight="1" s="21"/>
-    <row r="894" ht="15.75" customHeight="1" s="21"/>
-    <row r="895" ht="15.75" customHeight="1" s="21"/>
-    <row r="896" ht="15.75" customHeight="1" s="21"/>
-    <row r="897" ht="15.75" customHeight="1" s="21"/>
-    <row r="898" ht="15.75" customHeight="1" s="21"/>
-    <row r="899" ht="15.75" customHeight="1" s="21"/>
-    <row r="900" ht="15.75" customHeight="1" s="21"/>
-    <row r="901" ht="15.75" customHeight="1" s="21"/>
-    <row r="902" ht="15.75" customHeight="1" s="21"/>
-    <row r="903" ht="15.75" customHeight="1" s="21"/>
-    <row r="904" ht="15.75" customHeight="1" s="21"/>
-    <row r="905" ht="15.75" customHeight="1" s="21"/>
-    <row r="906" ht="15.75" customHeight="1" s="21"/>
-    <row r="907" ht="15.75" customHeight="1" s="21"/>
-    <row r="908" ht="15.75" customHeight="1" s="21"/>
-    <row r="909" ht="15.75" customHeight="1" s="21"/>
-    <row r="910" ht="15.75" customHeight="1" s="21"/>
-    <row r="911" ht="15.75" customHeight="1" s="21"/>
-    <row r="912" ht="15.75" customHeight="1" s="21"/>
-    <row r="913" ht="15.75" customHeight="1" s="21"/>
-    <row r="914" ht="15.75" customHeight="1" s="21"/>
-    <row r="915" ht="15.75" customHeight="1" s="21"/>
-    <row r="916" ht="15.75" customHeight="1" s="21"/>
-    <row r="917" ht="15.75" customHeight="1" s="21"/>
-    <row r="918" ht="15.75" customHeight="1" s="21"/>
-    <row r="919" ht="15.75" customHeight="1" s="21"/>
-    <row r="920" ht="15.75" customHeight="1" s="21"/>
-    <row r="921" ht="15.75" customHeight="1" s="21"/>
-    <row r="922" ht="15.75" customHeight="1" s="21"/>
-    <row r="923" ht="15.75" customHeight="1" s="21"/>
-    <row r="924" ht="15.75" customHeight="1" s="21"/>
-    <row r="925" ht="15.75" customHeight="1" s="21"/>
-    <row r="926" ht="15.75" customHeight="1" s="21"/>
-    <row r="927" ht="15.75" customHeight="1" s="21"/>
-    <row r="928" ht="15.75" customHeight="1" s="21"/>
-    <row r="929" ht="15.75" customHeight="1" s="21"/>
-    <row r="930" ht="15.75" customHeight="1" s="21"/>
-    <row r="931" ht="15.75" customHeight="1" s="21"/>
-    <row r="932" ht="15.75" customHeight="1" s="21"/>
-    <row r="933" ht="15.75" customHeight="1" s="21"/>
-    <row r="934" ht="15.75" customHeight="1" s="21"/>
-    <row r="935" ht="15.75" customHeight="1" s="21"/>
-    <row r="936" ht="15.75" customHeight="1" s="21"/>
-    <row r="937" ht="15.75" customHeight="1" s="21"/>
-    <row r="938" ht="15.75" customHeight="1" s="21"/>
-    <row r="939" ht="15.75" customHeight="1" s="21"/>
-    <row r="940" ht="15.75" customHeight="1" s="21"/>
-    <row r="941" ht="15.75" customHeight="1" s="21"/>
-    <row r="942" ht="15.75" customHeight="1" s="21"/>
-    <row r="943" ht="15.75" customHeight="1" s="21"/>
-    <row r="944" ht="15.75" customHeight="1" s="21"/>
-    <row r="945" ht="15.75" customHeight="1" s="21"/>
-    <row r="946" ht="15.75" customHeight="1" s="21"/>
-    <row r="947" ht="15.75" customHeight="1" s="21"/>
-    <row r="948" ht="15.75" customHeight="1" s="21"/>
-    <row r="949" ht="15.75" customHeight="1" s="21"/>
-    <row r="950" ht="15.75" customHeight="1" s="21"/>
-    <row r="951" ht="15.75" customHeight="1" s="21"/>
-    <row r="952" ht="15.75" customHeight="1" s="21"/>
-    <row r="953" ht="15.75" customHeight="1" s="21"/>
-    <row r="954" ht="15.75" customHeight="1" s="21"/>
-    <row r="955" ht="15.75" customHeight="1" s="21"/>
-    <row r="956" ht="15.75" customHeight="1" s="21"/>
-    <row r="957" ht="15.75" customHeight="1" s="21"/>
-    <row r="958" ht="15.75" customHeight="1" s="21"/>
-    <row r="959" ht="15.75" customHeight="1" s="21"/>
-    <row r="960" ht="15.75" customHeight="1" s="21"/>
-    <row r="961" ht="15.75" customHeight="1" s="21"/>
-    <row r="962" ht="15.75" customHeight="1" s="21"/>
-    <row r="963" ht="15.75" customHeight="1" s="21"/>
-    <row r="964" ht="15.75" customHeight="1" s="21"/>
-    <row r="965" ht="15.75" customHeight="1" s="21"/>
-    <row r="966" ht="15.75" customHeight="1" s="21"/>
-    <row r="967" ht="15.75" customHeight="1" s="21"/>
-    <row r="968" ht="15.75" customHeight="1" s="21"/>
-    <row r="969" ht="15.75" customHeight="1" s="21"/>
-    <row r="970" ht="15.75" customHeight="1" s="21"/>
-    <row r="971" ht="15.75" customHeight="1" s="21"/>
-    <row r="972" ht="15.75" customHeight="1" s="21"/>
-    <row r="973" ht="15.75" customHeight="1" s="21"/>
-    <row r="974" ht="15.75" customHeight="1" s="21"/>
-    <row r="975" ht="15.75" customHeight="1" s="21"/>
-    <row r="976" ht="15.75" customHeight="1" s="21"/>
-    <row r="977" ht="15.75" customHeight="1" s="21"/>
-    <row r="978" ht="15.75" customHeight="1" s="21"/>
-    <row r="979" ht="15.75" customHeight="1" s="21"/>
-    <row r="980" ht="15.75" customHeight="1" s="21"/>
-    <row r="981" ht="15.75" customHeight="1" s="21"/>
-    <row r="982" ht="15.75" customHeight="1" s="21"/>
-    <row r="983" ht="15.75" customHeight="1" s="21"/>
-    <row r="984" ht="15.75" customHeight="1" s="21"/>
-    <row r="985" ht="15.75" customHeight="1" s="21"/>
-    <row r="986" ht="15.75" customHeight="1" s="21"/>
-    <row r="987" ht="15.75" customHeight="1" s="21"/>
-    <row r="988" ht="15.75" customHeight="1" s="21"/>
-    <row r="989" ht="15.75" customHeight="1" s="21"/>
-    <row r="990" ht="15.75" customHeight="1" s="21"/>
-    <row r="991" ht="15.75" customHeight="1" s="21"/>
-    <row r="992" ht="15.75" customHeight="1" s="21"/>
-    <row r="993" ht="15.75" customHeight="1" s="21"/>
-    <row r="994" ht="15.75" customHeight="1" s="21"/>
-    <row r="995" ht="15.75" customHeight="1" s="21"/>
-    <row r="996" ht="15.75" customHeight="1" s="21"/>
-    <row r="997" ht="15.75" customHeight="1" s="21"/>
-    <row r="998" ht="15.75" customHeight="1" s="21"/>
-    <row r="999" ht="15.75" customHeight="1" s="21"/>
-    <row r="1000" ht="15.75" customHeight="1" s="21"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
